--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED110E08-BAAB-4F81-8CAD-250C558B7567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2818E6-CD1A-406B-98B2-FCC508E244E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46260</v>
+        <v>46281</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55638,7 +55638,7 @@
         <v>4503.8973958178003</v>
       </c>
       <c r="E1214" s="36">
-        <v>4602.0452868263301</v>
+        <v>4602.0452868263292</v>
       </c>
       <c r="F1214" s="35">
         <v>2171.1239</v>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164400000009</v>
+        <v>76699.164399999994</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.5969827764493</v>
+        <v>4600.5969827764484</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.675999999999</v>
+        <v>62640.676000000007</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320599999992</v>
+        <v>68594.320600000006</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313499999997</v>
+        <v>52967.313500000004</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56419,7 +56419,7 @@
       <c r="L1234" s="35"/>
       <c r="M1234" s="35"/>
       <c r="N1234" s="37">
-        <v>43632.772699999994</v>
+        <v>43632.772700000001</v>
       </c>
     </row>
     <row r="1235" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359399999994</v>
+        <v>53725.359400000001</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703700000005</v>
+        <v>57650.703699999998</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639500000005</v>
+        <v>48636.639499999997</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56905,7 +56905,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5394.2932473875308</v>
+        <v>5394.2932473875317</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -56931,7 +56931,7 @@
         <v>4658.6445909997819</v>
       </c>
       <c r="E1248" s="36">
-        <v>5064.4315799785836</v>
+        <v>5064.4315799785845</v>
       </c>
       <c r="F1248" s="35">
         <v>1018.4743</v>
@@ -57066,7 +57066,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>60820.301899999999</v>
+        <v>60820.301900000006</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57150,16 +57150,16 @@
         <v>45976</v>
       </c>
       <c r="B1254" s="35">
-        <v>45068.991300000002</v>
+        <v>45068.890299999999</v>
       </c>
       <c r="C1254" s="35">
         <v>8932.4151000000002</v>
       </c>
       <c r="D1254" s="35">
-        <v>5045.5549585912104</v>
+        <v>5045.5436514588309</v>
       </c>
       <c r="E1254" s="36">
-        <v>5297.0249451096579</v>
+        <v>5297.0227421104519</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57180,7 +57180,7 @@
       <c r="L1254" s="35"/>
       <c r="M1254" s="35"/>
       <c r="N1254" s="37">
-        <v>57860.842400000001</v>
+        <v>57860.741399999999</v>
       </c>
     </row>
     <row r="1255" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57197,7 +57197,7 @@
         <v>6208.4439483334208</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.3411260737348</v>
+        <v>5572.3392914722635</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371008</v>
+        <v>5978.5241558371017</v>
       </c>
       <c r="J1255" s="35">
         <v>12540.7538</v>
@@ -57218,7 +57218,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99670.855500000005</v>
+        <v>99670.855499999991</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57226,16 +57226,16 @@
         <v>45990</v>
       </c>
       <c r="B1256" s="35">
-        <v>64982.8246</v>
+        <v>64981.677900000002</v>
       </c>
       <c r="C1256" s="35">
         <v>12531.0414</v>
       </c>
       <c r="D1256" s="35">
-        <v>5185.7481374213639</v>
+        <v>5185.6566286661546</v>
       </c>
       <c r="E1256" s="36">
-        <v>5466.938643722704</v>
+        <v>5466.9173411825122</v>
       </c>
       <c r="F1256" s="35">
         <v>3141.94</v>
@@ -57247,7 +57247,7 @@
         <v>7229.0792158393024</v>
       </c>
       <c r="I1256" s="36">
-        <v>6258.6852471244501</v>
+        <v>6258.6852471244511</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.1422999999995</v>
@@ -57256,7 +57256,7 @@
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77367.906900000002</v>
+        <v>77366.760200000004</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57273,7 +57273,7 @@
         <v>5244.3681512482881</v>
       </c>
       <c r="E1257" s="36">
-        <v>5418.4771986673286</v>
+        <v>5418.4540805354673</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57285,7 +57285,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6857.6810418042396</v>
+        <v>6857.6810418042405</v>
       </c>
       <c r="J1257" s="35">
         <v>7037.5686999999998</v>
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.358000000007</v>
+        <v>78641.357999999993</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57311,7 +57311,7 @@
         <v>4962.80776653056</v>
       </c>
       <c r="E1258" s="36">
-        <v>5447.3925382734687</v>
+        <v>5447.3710519934875</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75388.57699999999</v>
+        <v>75388.577000000005</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57349,7 +57349,7 @@
         <v>5451.7744802757134</v>
       </c>
       <c r="E1259" s="36">
-        <v>5177.950684360675</v>
+        <v>5177.9288325754933</v>
       </c>
       <c r="F1259" s="35">
         <v>3014.4270000000001</v>
@@ -57387,7 +57387,7 @@
         <v>5176.6167478837451</v>
       </c>
       <c r="E1260" s="36">
-        <v>5202.9541683524567</v>
+        <v>5202.9318260556556</v>
       </c>
       <c r="F1260" s="35">
         <v>2192.3276999999998</v>
@@ -57463,7 +57463,7 @@
         <v>5564.1977074457418</v>
       </c>
       <c r="E1262" s="36">
-        <v>5249.7384184642124</v>
+        <v>5249.7384184642106</v>
       </c>
       <c r="F1262" s="35">
         <v>1210.1021000000001</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796990993</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57644,16 +57644,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77370.473400000003</v>
+        <v>77369.701400000005</v>
       </c>
       <c r="C1267" s="40">
         <v>13530.0152</v>
       </c>
       <c r="D1267" s="40">
-        <v>5718.4321123305172</v>
+        <v>5718.3750540058527</v>
       </c>
       <c r="E1267" s="41">
-        <v>5388.3527038829152</v>
+        <v>5388.3367183836017</v>
       </c>
       <c r="F1267" s="40">
         <v>1828.6121000000001</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92445.545800000007</v>
+        <v>92444.77380000001</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57691,7 +57691,7 @@
         <v>5134.4248379966566</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.6814768159466</v>
+        <v>5333.6663096193315</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57729,7 +57729,7 @@
         <v>5300.0847228510156</v>
       </c>
       <c r="E1269" s="41">
-        <v>5319.1692744618276</v>
+        <v>5319.1539472201748</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57767,7 +57767,7 @@
         <v>5924.9413302489766</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.6888171676719</v>
+        <v>5432.6737090924162</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57805,7 +57805,7 @@
         <v>5455.7971255995071</v>
       </c>
       <c r="E1271" s="41">
-        <v>5413.0949188940249</v>
+        <v>5413.0791506838395</v>
       </c>
       <c r="F1271" s="40">
         <v>1806.9168</v>
@@ -57881,7 +57881,7 @@
         <v>5733.4840776848541</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.7616187870799</v>
+        <v>5668.761618787079</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57910,16 +57910,16 @@
         <v>46116</v>
       </c>
       <c r="B1274" s="40">
-        <v>52059.355900000002</v>
+        <v>51999.285000000003</v>
       </c>
       <c r="C1274" s="40">
         <v>9635.9233000000004</v>
       </c>
       <c r="D1274" s="40">
-        <v>5402.63286446043</v>
+        <v>5396.3988069518982</v>
       </c>
       <c r="E1274" s="41">
-        <v>5579.4295053700225</v>
+        <v>5577.9970067451304</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.5085999999999</v>
@@ -57940,7 +57940,7 @@
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61574.915400000005</v>
+        <v>61514.844500000007</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57948,16 +57948,16 @@
         <v>46123</v>
       </c>
       <c r="B1275" s="40">
-        <v>25430.074199999999</v>
+        <v>25430.0023</v>
       </c>
       <c r="C1275" s="40">
         <v>4164.0848999999998</v>
       </c>
       <c r="D1275" s="40">
-        <v>6107.0018529161116</v>
+        <v>6106.9845862172506</v>
       </c>
       <c r="E1275" s="41">
-        <v>5669.7570862733501</v>
+        <v>5668.1234508569378</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57978,7 +57978,7 @@
       <c r="L1275" s="40"/>
       <c r="M1275" s="40"/>
       <c r="N1275" s="40">
-        <v>30621.0494</v>
+        <v>30620.977500000001</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57995,7 +57995,7 @@
         <v>5803.5857402637548</v>
       </c>
       <c r="E1276" s="41">
-        <v>5698.3072775989513</v>
+        <v>5696.5741065282946</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58033,7 +58033,7 @@
         <v>5849.5952010679366</v>
       </c>
       <c r="E1277" s="41">
-        <v>5646.1894176170217</v>
+        <v>5644.3315736110926</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58062,16 +58062,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>29407.9486</v>
+        <v>29407.607800000002</v>
       </c>
       <c r="C1278" s="40">
         <v>5721.3356999999996</v>
       </c>
       <c r="D1278" s="40">
-        <v>5140.0494818019515</v>
+        <v>5139.9899152919834</v>
       </c>
       <c r="E1278" s="41">
-        <v>5541.9614999797677</v>
+        <v>5541.9470694330748</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42470.883900000001</v>
+        <v>42470.543100000003</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58100,16 +58100,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>33626.934300000001</v>
+        <v>33626.859199999999</v>
       </c>
       <c r="C1279" s="40">
         <v>5126.8805000000002</v>
       </c>
       <c r="D1279" s="40">
-        <v>6558.946380747514</v>
+        <v>6558.9317324638232</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.7609552591903</v>
+        <v>5769.7451271633172</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58130,7 +58130,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>38913.010900000001</v>
+        <v>38912.935799999999</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58147,7 +58147,7 @@
         <v>6539.6430541936406</v>
       </c>
       <c r="E1280" s="41">
-        <v>6016.1433583652197</v>
+        <v>6016.1286399504188</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58176,16 +58176,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>57163.490899999997</v>
+        <v>57163.340600000003</v>
       </c>
       <c r="C1281" s="40">
         <v>8446.8318999999992</v>
       </c>
       <c r="D1281" s="40">
-        <v>6767.4474378968052</v>
+        <v>6767.429644243306</v>
       </c>
       <c r="E1281" s="41">
-        <v>6315.9646536421196</v>
+        <v>6315.9454622851645</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58206,7 +58206,7 @@
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>65014.249299999996</v>
+        <v>65014.099000000002</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58223,7 +58223,7 @@
         <v>5619.2449669061098</v>
       </c>
       <c r="E1282" s="41">
-        <v>6315.2651935055219</v>
+        <v>6315.2586998305105</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76963.001600000003</v>
+        <v>76963.001599999989</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58261,7 +58261,7 @@
         <v>5590.4628647718337</v>
       </c>
       <c r="E1283" s="41">
-        <v>6032.5665659862752</v>
+        <v>6032.5629444241631</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58282,7 +58282,7 @@
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>71799.068699999989</v>
+        <v>71799.068700000003</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58299,7 +58299,7 @@
         <v>6335.6880909849342</v>
       </c>
       <c r="E1284" s="41">
-        <v>5949.899381198391</v>
+        <v>5949.8957623713368</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62178.606800000001</v>
+        <v>62178.531900000002</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6203.8949060601217</v>
+        <v>6203.8874328832135</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.2956349021733</v>
+        <v>5860.2939760135632</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58396,7 +58396,7 @@
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69942.548200000005</v>
+        <v>69942.473299999998</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58413,7 +58413,7 @@
         <v>6389.8389410197242</v>
       </c>
       <c r="E1287" s="41">
-        <v>6051.909912421399</v>
+        <v>6051.9079001380233</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
@@ -58436,16 +58436,16 @@
         <v>46214</v>
       </c>
       <c r="B1288" s="40">
-        <v>68436.839699999997</v>
+        <v>68436.839800000002</v>
       </c>
       <c r="C1288" s="40">
         <v>11480.580099999999</v>
       </c>
       <c r="D1288" s="40">
-        <v>5961.0959641316385</v>
+        <v>5961.0959728419994</v>
       </c>
       <c r="E1288" s="41">
-        <v>6090.4018576942317</v>
+        <v>6090.4000146556054</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58466,7 +58466,7 @@
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>77063.173599999995</v>
+        <v>77063.173699999999</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58474,16 +58474,16 @@
         <v>46221</v>
       </c>
       <c r="B1289" s="40">
-        <v>43928.746599999999</v>
+        <v>43928.746700000003</v>
       </c>
       <c r="C1289" s="40">
         <v>7626.7623999999996</v>
       </c>
       <c r="D1289" s="40">
-        <v>5759.8158033610698</v>
+        <v>5759.8158164727938</v>
       </c>
       <c r="E1289" s="41">
-        <v>6048.2971729571036</v>
+        <v>6048.2952787262766</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58504,7 +58504,7 @@
       <c r="L1289" s="40"/>
       <c r="M1289" s="40"/>
       <c r="N1289" s="40">
-        <v>49856.339599999999</v>
+        <v>49856.339700000004</v>
       </c>
     </row>
     <row r="1290" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58512,16 +58512,16 @@
         <v>46228</v>
       </c>
       <c r="B1290" s="40">
-        <v>79759.197799999994</v>
+        <v>79759.197700000004</v>
       </c>
       <c r="C1290" s="40">
         <v>13474.185299999999</v>
       </c>
       <c r="D1290" s="40">
-        <v>5919.4078175546538</v>
+        <v>5919.4078101330551</v>
       </c>
       <c r="E1290" s="41">
-        <v>6030.6903550355928</v>
+        <v>6030.6886295454078</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58542,7 +58542,7 @@
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86936.970599999986</v>
+        <v>86936.97050000001</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58550,16 +58550,16 @@
         <v>46235</v>
       </c>
       <c r="B1291" s="40">
-        <v>57770.960500000001</v>
+        <v>57773.6322</v>
       </c>
       <c r="C1291" s="40">
         <v>10083.671899999999</v>
       </c>
       <c r="D1291" s="40">
-        <v>5729.1590873757013</v>
+        <v>5729.4240404628799</v>
       </c>
       <c r="E1291" s="41">
-        <v>5929.9488439476581</v>
+        <v>5930.009020993718</v>
       </c>
       <c r="F1291" s="40">
         <v>1001.2517</v>
@@ -58580,7 +58580,7 @@
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>71055.878599999996</v>
+        <v>71058.550300000003</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58597,7 +58597,7 @@
         <v>6399.802136951751</v>
       </c>
       <c r="E1292" s="41">
-        <v>5962.201993265704</v>
+        <v>5962.2579663153774</v>
       </c>
       <c r="F1292" s="40">
         <v>278.08030000000002</v>
@@ -58635,7 +58635,7 @@
         <v>6332.1775899330314</v>
       </c>
       <c r="E1293" s="41">
-        <v>6093.2215939903417</v>
+        <v>6093.2792615086719</v>
       </c>
       <c r="F1293" s="40">
         <v>348.17270000000002</v>
@@ -58664,16 +58664,16 @@
         <v>46256</v>
       </c>
       <c r="B1294" s="40">
-        <v>65658.519100000005</v>
+        <v>67790.628200000006</v>
       </c>
       <c r="C1294" s="40">
-        <v>11053.063700000001</v>
+        <v>11349.038200000001</v>
       </c>
       <c r="D1294" s="40">
-        <v>5940.3004345302015</v>
+        <v>5973.2487463122643</v>
       </c>
       <c r="E1294" s="41">
-        <v>6165.7980621688976</v>
+        <v>6172.3914096673579</v>
       </c>
       <c r="F1294" s="40">
         <v>922.0231</v>
@@ -58688,13 +58688,13 @@
         <v>5774.2266878472819</v>
       </c>
       <c r="J1294" s="40">
-        <v>11193.4807</v>
+        <v>11287.036599999999</v>
       </c>
       <c r="K1294" s="40"/>
       <c r="L1294" s="40"/>
       <c r="M1294" s="40"/>
       <c r="N1294" s="40">
-        <v>77774.022900000011</v>
+        <v>79999.687900000004</v>
       </c>
     </row>
     <row r="1295" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58702,37 +58702,37 @@
         <v>46263</v>
       </c>
       <c r="B1295" s="40">
-        <v>26805.156299999999</v>
+        <v>29855.5124</v>
       </c>
       <c r="C1295" s="40">
-        <v>4193.8714</v>
+        <v>4675.8275000000003</v>
       </c>
       <c r="D1295" s="40">
-        <v>6391.5064968372653</v>
+        <v>6385.0756684244652</v>
       </c>
       <c r="E1295" s="41">
-        <v>6113.8699304593802</v>
+        <v>6124.022454842413</v>
       </c>
       <c r="F1295" s="40">
         <v>1206.4709</v>
       </c>
       <c r="G1295" s="40">
-        <v>137.66929999999999</v>
+        <v>136.90430000000001</v>
       </c>
       <c r="H1295" s="40">
-        <v>8763.5435060685286</v>
+        <v>8812.5128283041522</v>
       </c>
       <c r="I1295" s="41">
-        <v>6351.4475282341673</v>
+        <v>6360.5383082196067</v>
       </c>
       <c r="J1295" s="40">
-        <v>3115.2201</v>
+        <v>3095.3777</v>
       </c>
       <c r="K1295" s="40"/>
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
       <c r="N1295" s="40">
-        <v>31126.847299999998</v>
+        <v>34157.360999999997</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58740,48 +58740,76 @@
         <v>46270</v>
       </c>
       <c r="B1296" s="40">
-        <v>51450.369899999998</v>
+        <v>64635.974600000001</v>
       </c>
       <c r="C1296" s="40">
-        <v>9005.3593000000001</v>
+        <v>11466.340399999999</v>
       </c>
       <c r="D1296" s="40">
-        <v>5713.3056201322252</v>
+        <v>5637.0186428444076</v>
       </c>
       <c r="E1296" s="41">
-        <v>6218.661212658998</v>
-      </c>
-      <c r="F1296" s="40"/>
-      <c r="G1296" s="40"/>
-      <c r="H1296" s="40"/>
+        <v>6174.9463038232479</v>
+      </c>
+      <c r="F1296" s="40">
+        <v>91.807299999999998</v>
+      </c>
+      <c r="G1296" s="40">
+        <v>18.0245</v>
+      </c>
+      <c r="H1296" s="40">
+        <v>5093.4727731698522</v>
+      </c>
       <c r="I1296" s="41">
-        <v>6383.1945010025829</v>
+        <v>6337.8814704231263</v>
       </c>
       <c r="J1296" s="40">
-        <v>4599.5405000000001</v>
+        <v>5207.4573</v>
       </c>
       <c r="K1296" s="40"/>
       <c r="L1296" s="40"/>
       <c r="M1296" s="40"/>
       <c r="N1296" s="40">
-        <v>56049.910400000001</v>
+        <v>69935.239199999996</v>
       </c>
     </row>
     <row r="1297" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1297" s="39"/>
-      <c r="B1297" s="40"/>
-      <c r="C1297" s="40"/>
-      <c r="D1297" s="40"/>
-      <c r="E1297" s="41"/>
-      <c r="F1297" s="40"/>
-      <c r="G1297" s="40"/>
-      <c r="H1297" s="40"/>
-      <c r="I1297" s="41"/>
-      <c r="J1297" s="40"/>
+      <c r="A1297" s="39">
+        <v>46277</v>
+      </c>
+      <c r="B1297" s="40">
+        <v>38252.554900000003</v>
+      </c>
+      <c r="C1297" s="40">
+        <v>5678.1174000000001</v>
+      </c>
+      <c r="D1297" s="40">
+        <v>6736.837618045729</v>
+      </c>
+      <c r="E1297" s="41">
+        <v>6224.9512190328269</v>
+      </c>
+      <c r="F1297" s="40">
+        <v>105.6476</v>
+      </c>
+      <c r="G1297" s="40">
+        <v>21.582899999999999</v>
+      </c>
+      <c r="H1297" s="40">
+        <v>4894.9677754147961</v>
+      </c>
+      <c r="I1297" s="41">
+        <v>6394.3994579679566</v>
+      </c>
+      <c r="J1297" s="40">
+        <v>4120.7143999999998</v>
+      </c>
       <c r="K1297" s="40"/>
       <c r="L1297" s="40"/>
       <c r="M1297" s="40"/>
-      <c r="N1297" s="40"/>
+      <c r="N1297" s="40">
+        <v>42478.916900000004</v>
+      </c>
     </row>
     <row r="1298" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1298" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354DFBE6-3A6E-4445-AF7A-16550A79ED2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2DAEEE-1220-43BD-8FFA-A626A3BCCD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55486,7 +55486,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139713</v>
+        <v>4508.5895396139722</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55638,7 +55638,7 @@
         <v>4503.8973958178003</v>
       </c>
       <c r="E1214" s="36">
-        <v>4602.0452868263301</v>
+        <v>4602.0452868263292</v>
       </c>
       <c r="F1214" s="35">
         <v>2171.1239</v>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164399999994</v>
+        <v>76699.164400000009</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55676,7 +55676,7 @@
         <v>4524.9943499506198</v>
       </c>
       <c r="E1215" s="36">
-        <v>4600.5969827764493</v>
+        <v>4600.5969827764484</v>
       </c>
       <c r="F1215" s="35">
         <v>1717.5505000000001</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888563</v>
+        <v>4764.4312599888553</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8123550761293</v>
+        <v>4705.8123550761284</v>
       </c>
       <c r="F1217" s="35">
         <v>1657.8610000000001</v>
@@ -55790,7 +55790,7 @@
         <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4735.8590672017526</v>
+        <v>4735.8590672017517</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.676000000007</v>
+        <v>62640.675999999999</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947385</v>
+        <v>4662.2080120947376</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -55904,7 +55904,7 @@
         <v>4701.7281140876712</v>
       </c>
       <c r="E1221" s="36">
-        <v>4669.4458132671598</v>
+        <v>4669.4458132671589</v>
       </c>
       <c r="F1221" s="35">
         <v>673.16070000000002</v>
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320600000006</v>
+        <v>68594.320599999992</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313500000004</v>
+        <v>52967.313499999997</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56237,16 +56237,16 @@
         <v>45808</v>
       </c>
       <c r="B1230" s="35">
-        <v>47051.885499999997</v>
+        <v>47047.374100000001</v>
       </c>
       <c r="C1230" s="35">
         <v>9007.6190000000006</v>
       </c>
       <c r="D1230" s="35">
-        <v>5223.5652396043834</v>
+        <v>5223.0643969288667</v>
       </c>
       <c r="E1230" s="36">
-        <v>5027.9793582030034</v>
+        <v>5027.8916316333225</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56267,7 +56267,7 @@
       <c r="L1230" s="35"/>
       <c r="M1230" s="35"/>
       <c r="N1230" s="37">
-        <v>52615.957299999995</v>
+        <v>52611.445899999999</v>
       </c>
     </row>
     <row r="1231" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56284,7 +56284,7 @@
         <v>4742.1060383005579</v>
       </c>
       <c r="E1231" s="36">
-        <v>4960.9505974298099</v>
+        <v>4960.8711832545605</v>
       </c>
       <c r="F1231" s="35">
         <v>1023.9116</v>
@@ -56322,7 +56322,7 @@
         <v>4822.0687291159447</v>
       </c>
       <c r="E1232" s="36">
-        <v>4909.2993048166982</v>
+        <v>4909.21113551505</v>
       </c>
       <c r="F1232" s="35">
         <v>1930.2304999999999</v>
@@ -56343,7 +56343,7 @@
       <c r="L1232" s="35"/>
       <c r="M1232" s="35"/>
       <c r="N1232" s="37">
-        <v>68154.185599999997</v>
+        <v>68154.185600000012</v>
       </c>
     </row>
     <row r="1233" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56360,7 +56360,7 @@
         <v>4913.6423627303329</v>
       </c>
       <c r="E1233" s="36">
-        <v>4835.8535729451951</v>
+        <v>4835.7591353285616</v>
       </c>
       <c r="F1233" s="35">
         <v>910.61059999999998</v>
@@ -56398,7 +56398,7 @@
         <v>4897.6606435012372</v>
       </c>
       <c r="E1234" s="36">
-        <v>4765.808222470997</v>
+        <v>4765.8082224709979</v>
       </c>
       <c r="F1234" s="35">
         <v>556.48080000000004</v>
@@ -56419,7 +56419,7 @@
       <c r="L1234" s="35"/>
       <c r="M1234" s="35"/>
       <c r="N1234" s="37">
-        <v>43632.772700000001</v>
+        <v>43632.772699999994</v>
       </c>
     </row>
     <row r="1235" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56436,7 +56436,7 @@
         <v>5123.1647487932232</v>
       </c>
       <c r="E1235" s="36">
-        <v>4954.1827371364479</v>
+        <v>4954.1827371364488</v>
       </c>
       <c r="F1235" s="35">
         <v>1182.9712999999999</v>
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359400000001</v>
+        <v>53725.359399999994</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56588,7 +56588,7 @@
         <v>5020.0251051799696</v>
       </c>
       <c r="E1239" s="36">
-        <v>4983.5092802101408</v>
+        <v>4983.509280210139</v>
       </c>
       <c r="F1239" s="35">
         <v>1951.8497</v>
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703699999998</v>
+        <v>57650.703700000005</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6129.9007248539556</v>
+        <v>6129.9007248539547</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639499999997</v>
+        <v>48636.639500000005</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56905,7 +56905,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5388.6606709613825</v>
+        <v>5388.6606709613816</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -56922,16 +56922,16 @@
         <v>45934</v>
       </c>
       <c r="B1248" s="35">
-        <v>34613.0389</v>
+        <v>34610.5026</v>
       </c>
       <c r="C1248" s="35">
         <v>7429.8518000000004</v>
       </c>
       <c r="D1248" s="35">
-        <v>4658.6445909997819</v>
+        <v>4658.3032248368672</v>
       </c>
       <c r="E1248" s="36">
-        <v>5064.4315799785836</v>
+        <v>5064.3663495203118</v>
       </c>
       <c r="F1248" s="35">
         <v>1018.4743</v>
@@ -56952,7 +56952,7 @@
       <c r="L1248" s="35"/>
       <c r="M1248" s="35"/>
       <c r="N1248" s="37">
-        <v>40360.017200000002</v>
+        <v>40357.480900000002</v>
       </c>
     </row>
     <row r="1249" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56960,16 +56960,16 @@
         <v>45941</v>
       </c>
       <c r="B1249" s="35">
-        <v>24109.5556</v>
+        <v>24109.048299999999</v>
       </c>
       <c r="C1249" s="35">
         <v>5500.9261999999999</v>
       </c>
       <c r="D1249" s="35">
-        <v>4382.8174971698409</v>
+        <v>4382.7252763361921</v>
       </c>
       <c r="E1249" s="36">
-        <v>4972.2196515399091</v>
+        <v>4972.1379847864046</v>
       </c>
       <c r="F1249" s="35">
         <v>1116.6591000000001</v>
@@ -56990,7 +56990,7 @@
       <c r="L1249" s="35"/>
       <c r="M1249" s="35"/>
       <c r="N1249" s="37">
-        <v>31426.6139</v>
+        <v>31426.106599999999</v>
       </c>
     </row>
     <row r="1250" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56998,16 +56998,16 @@
         <v>45948</v>
       </c>
       <c r="B1250" s="35">
-        <v>48095.381600000001</v>
+        <v>48095.127999999997</v>
       </c>
       <c r="C1250" s="35">
         <v>9753.8886999999995</v>
       </c>
       <c r="D1250" s="35">
-        <v>4930.8930088570733</v>
+        <v>4930.8670089704838</v>
       </c>
       <c r="E1250" s="36">
-        <v>4940.3686918435942</v>
+        <v>4940.2788318269786</v>
       </c>
       <c r="F1250" s="35">
         <v>1339.0517</v>
@@ -57028,7 +57028,7 @@
       <c r="L1250" s="35"/>
       <c r="M1250" s="35"/>
       <c r="N1250" s="37">
-        <v>61868.9231</v>
+        <v>61868.669499999989</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57036,16 +57036,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="35">
-        <v>54246.384400000003</v>
+        <v>54245.623500000002</v>
       </c>
       <c r="C1251" s="35">
         <v>9527.3052000000007</v>
       </c>
       <c r="D1251" s="35">
-        <v>5693.7804826489655</v>
+        <v>5693.7006174631624</v>
       </c>
       <c r="E1251" s="36">
-        <v>5005.8415441462721</v>
+        <v>5005.7288484653054</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57066,7 +57066,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>60820.301900000006</v>
+        <v>60819.540999999997</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57074,16 +57074,16 @@
         <v>45962</v>
       </c>
       <c r="B1252" s="35">
-        <v>49049.208299999998</v>
+        <v>49048.063199999997</v>
       </c>
       <c r="C1252" s="35">
         <v>10403.208199999999</v>
       </c>
       <c r="D1252" s="35">
-        <v>4714.8155989034231</v>
+        <v>4714.7055270892297</v>
       </c>
       <c r="E1252" s="36">
-        <v>4978.9598424893193</v>
+        <v>4978.8868075822375</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57104,7 +57104,7 @@
       <c r="L1252" s="35"/>
       <c r="M1252" s="35"/>
       <c r="N1252" s="37">
-        <v>60801.436999999998</v>
+        <v>60800.291899999997</v>
       </c>
     </row>
     <row r="1253" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57121,7 +57121,7 @@
         <v>5679.5787797836083</v>
       </c>
       <c r="E1253" s="36">
-        <v>5193.2954400815997</v>
+        <v>5193.2421766004063</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57159,7 +57159,7 @@
         <v>5045.5436514588309</v>
       </c>
       <c r="E1254" s="36">
-        <v>5297.0227421104519</v>
+        <v>5296.9811686799094</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57197,7 +57197,7 @@
         <v>6207.5247210090993</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.1123458209104</v>
+        <v>5572.0777245297722</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371017</v>
+        <v>5978.5241558371008</v>
       </c>
       <c r="J1255" s="35">
         <v>12540.7538</v>
@@ -57218,7 +57218,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99658.361499999999</v>
+        <v>99658.361500000014</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57235,7 +57235,7 @@
         <v>5185.5703229900746</v>
       </c>
       <c r="E1256" s="36">
-        <v>5466.6855605987375</v>
+        <v>5466.6660097942377</v>
       </c>
       <c r="F1256" s="35">
         <v>3139.7898</v>
@@ -57247,16 +57247,16 @@
         <v>7224.1319647365126</v>
       </c>
       <c r="I1256" s="36">
-        <v>6257.5010579608343</v>
+        <v>6257.5010579608352</v>
       </c>
       <c r="J1256" s="35">
-        <v>9245.2924999999996</v>
+        <v>9243.7037999999993</v>
       </c>
       <c r="K1256" s="35"/>
       <c r="L1256" s="35"/>
       <c r="M1256" s="35"/>
       <c r="N1256" s="37">
-        <v>77365.678700000004</v>
+        <v>77364.09</v>
       </c>
     </row>
     <row r="1257" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57285,7 +57285,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6856.4662016578122</v>
+        <v>6856.4662016578131</v>
       </c>
       <c r="J1257" s="35">
         <v>7037.5686999999998</v>
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.357999999993</v>
+        <v>78641.358000000007</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75388.577000000005</v>
+        <v>75388.57699999999</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57399,7 +57399,7 @@
         <v>4873.0105884306095</v>
       </c>
       <c r="I1260" s="36">
-        <v>6633.6514180995446</v>
+        <v>6633.6514180995455</v>
       </c>
       <c r="J1260" s="35">
         <v>7680.5316000000003</v>
@@ -57437,7 +57437,7 @@
         <v>4523.51742353193</v>
       </c>
       <c r="I1261" s="36">
-        <v>6386.030925603357</v>
+        <v>6386.0309256033561</v>
       </c>
       <c r="J1261" s="35">
         <v>15412.583500000001</v>
@@ -57492,16 +57492,16 @@
         <v>46039</v>
       </c>
       <c r="B1263" s="35">
-        <v>58956.644500000002</v>
+        <v>58961.654300000002</v>
       </c>
       <c r="C1263" s="35">
         <v>11294.476500000001</v>
       </c>
       <c r="D1263" s="35">
-        <v>5219.953709231233</v>
+        <v>5220.3972711794122</v>
       </c>
       <c r="E1263" s="36">
-        <v>5329.80592858609</v>
+        <v>5329.9273081101001</v>
       </c>
       <c r="F1263" s="35">
         <v>3099.3226</v>
@@ -57513,16 +57513,16 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6202.638687550686</v>
+        <v>6202.6386875506842</v>
       </c>
       <c r="J1263" s="35">
-        <v>7879.2038000000002</v>
+        <v>7841.0056000000004</v>
       </c>
       <c r="K1263" s="35"/>
       <c r="L1263" s="35"/>
       <c r="M1263" s="35"/>
       <c r="N1263" s="37">
-        <v>69935.170899999997</v>
+        <v>69901.982499999998</v>
       </c>
     </row>
     <row r="1264" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57539,7 +57539,7 @@
         <v>5644.0828935425825</v>
       </c>
       <c r="E1264" s="36">
-        <v>5397.6711794434723</v>
+        <v>5397.8152706322044</v>
       </c>
       <c r="F1264" s="35">
         <v>1803.3380999999999</v>
@@ -57568,16 +57568,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66535.083499999993</v>
+        <v>66533.447499999995</v>
       </c>
       <c r="C1265" s="40">
         <v>12751.894200000001</v>
       </c>
       <c r="D1265" s="40">
-        <v>5217.6627610351397</v>
+        <v>5217.5344663697088</v>
       </c>
       <c r="E1265" s="41">
-        <v>5316.2431063253489</v>
+        <v>5316.3271849422181</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796990993</v>
+        <v>6791.398179699102</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57598,7 +57598,7 @@
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77714.050199999998</v>
+        <v>77712.414199999985</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.2081196023264</v>
+        <v>5320.2886080203034</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57644,16 +57644,16 @@
         <v>46067</v>
       </c>
       <c r="B1267" s="40">
-        <v>77369.701400000005</v>
+        <v>77368.023100000006</v>
       </c>
       <c r="C1267" s="40">
         <v>13530.0152</v>
       </c>
       <c r="D1267" s="40">
-        <v>5718.3750540058527</v>
+        <v>5718.2510112775044</v>
       </c>
       <c r="E1267" s="41">
-        <v>5387.9582057795224</v>
+        <v>5387.993313828857</v>
       </c>
       <c r="F1267" s="40">
         <v>1822.9809</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92444.77380000001</v>
+        <v>92443.095499999996</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57682,16 +57682,16 @@
         <v>46074</v>
       </c>
       <c r="B1268" s="40">
-        <v>65030.375500000002</v>
+        <v>65029.443099999997</v>
       </c>
       <c r="C1268" s="40">
         <v>12665.788</v>
       </c>
       <c r="D1268" s="40">
-        <v>5134.3331737433155</v>
+        <v>5134.2595581103988</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.5519898218517</v>
+        <v>5333.4685564878391</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81330.535499999998</v>
+        <v>81329.603100000008</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57729,7 +57729,7 @@
         <v>5300.0847228510156</v>
       </c>
       <c r="E1269" s="41">
-        <v>5319.1308967958767</v>
+        <v>5319.0465830690327</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57767,7 +57767,7 @@
         <v>5924.9413302489766</v>
       </c>
       <c r="E1270" s="41">
-        <v>5432.6509882693981</v>
+        <v>5432.5998967511778</v>
       </c>
       <c r="F1270" s="40">
         <v>1172.5832</v>
@@ -57805,7 +57805,7 @@
         <v>5455.7971255995071</v>
       </c>
       <c r="E1271" s="41">
-        <v>5413.0554370931313</v>
+        <v>5413.0021131730109</v>
       </c>
       <c r="F1271" s="40">
         <v>1801.3982000000001</v>
@@ -57817,7 +57817,7 @@
         <v>7025.7066080085497</v>
       </c>
       <c r="I1271" s="41">
-        <v>7474.9950981706652</v>
+        <v>7474.9950981706661</v>
       </c>
       <c r="J1271" s="40">
         <v>9744.1470000000008</v>
@@ -57843,7 +57843,7 @@
         <v>6070.5855710333217</v>
       </c>
       <c r="E1272" s="41">
-        <v>5601.9808830701886</v>
+        <v>5601.9808830701877</v>
       </c>
       <c r="F1272" s="40">
         <v>697.31119999999999</v>
@@ -57858,13 +57858,13 @@
         <v>7295.8626818021394</v>
       </c>
       <c r="J1272" s="40">
-        <v>7915.2548999999999</v>
+        <v>8013.4634999999998</v>
       </c>
       <c r="K1272" s="40"/>
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>45985.741899999994</v>
+        <v>46083.950499999992</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57919,7 +57919,7 @@
         <v>5396.3988069518982</v>
       </c>
       <c r="E1274" s="41">
-        <v>5577.9970067451304</v>
+        <v>5577.9970067451313</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.5085999999999</v>
@@ -57957,7 +57957,7 @@
         <v>6106.9845862172506</v>
       </c>
       <c r="E1275" s="41">
-        <v>5668.123450856936</v>
+        <v>5668.1234508569378</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57986,16 +57986,16 @@
         <v>46130</v>
       </c>
       <c r="B1276" s="40">
-        <v>45552.934699999998</v>
+        <v>45552.381099999999</v>
       </c>
       <c r="C1276" s="40">
         <v>7849.1017000000002</v>
       </c>
       <c r="D1276" s="40">
-        <v>5803.5857402637548</v>
+        <v>5803.5152098997523</v>
       </c>
       <c r="E1276" s="41">
-        <v>5696.5741065282946</v>
+        <v>5696.558153105696</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58010,13 +58010,13 @@
         <v>5606.7869431513891</v>
       </c>
       <c r="J1276" s="40">
-        <v>6631.9660000000003</v>
+        <v>6631.7284</v>
       </c>
       <c r="K1276" s="40"/>
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52468.070200000002</v>
+        <v>52467.279000000002</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58024,16 +58024,16 @@
         <v>46137</v>
       </c>
       <c r="B1277" s="40">
-        <v>32078.7127</v>
+        <v>32075.760300000002</v>
       </c>
       <c r="C1277" s="40">
         <v>5483.9201000000003</v>
       </c>
       <c r="D1277" s="40">
-        <v>5849.5952010679366</v>
+        <v>5849.0568270679214</v>
       </c>
       <c r="E1277" s="41">
-        <v>5644.3315736110926</v>
+        <v>5644.223271352389</v>
       </c>
       <c r="F1277" s="40">
         <v>577.98320000000001</v>
@@ -58054,7 +58054,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37839.5671</v>
+        <v>37836.614700000006</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58062,16 +58062,16 @@
         <v>46144</v>
       </c>
       <c r="B1278" s="40">
-        <v>29407.607800000002</v>
+        <v>29407.238700000002</v>
       </c>
       <c r="C1278" s="40">
         <v>5721.3356999999996</v>
       </c>
       <c r="D1278" s="40">
-        <v>5139.9899152919834</v>
+        <v>5139.9254023846224</v>
       </c>
       <c r="E1278" s="41">
-        <v>5541.9470694330739</v>
+        <v>5541.8115719494535</v>
       </c>
       <c r="F1278" s="40">
         <v>412.21159999999998</v>
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42470.543100000003</v>
+        <v>42470.174000000006</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58100,16 +58100,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>33626.859199999999</v>
+        <v>33626.428399999997</v>
       </c>
       <c r="C1279" s="40">
         <v>5126.8805000000002</v>
       </c>
       <c r="D1279" s="40">
-        <v>6558.9317324638232</v>
+        <v>6558.8477047592578</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.7451271633172</v>
+        <v>5769.5812555643333</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58130,7 +58130,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>38912.935799999999</v>
+        <v>38912.504999999997</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58138,16 +58138,16 @@
         <v>46158</v>
       </c>
       <c r="B1280" s="40">
-        <v>61456.328300000001</v>
+        <v>61405.843699999998</v>
       </c>
       <c r="C1280" s="40">
         <v>9397.5049999999992</v>
       </c>
       <c r="D1280" s="40">
-        <v>6539.6430541936406</v>
+        <v>6534.2709261660411</v>
       </c>
       <c r="E1280" s="41">
-        <v>6016.128639950417</v>
+        <v>6014.1896418591386</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58168,7 +58168,7 @@
       <c r="L1280" s="40"/>
       <c r="M1280" s="40"/>
       <c r="N1280" s="40">
-        <v>67729.820699999997</v>
+        <v>67679.3361</v>
       </c>
     </row>
     <row r="1281" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58176,16 +58176,16 @@
         <v>46165</v>
       </c>
       <c r="B1281" s="40">
-        <v>57129.908900000002</v>
+        <v>57129.627699999997</v>
       </c>
       <c r="C1281" s="40">
         <v>8446.8318999999992</v>
       </c>
       <c r="D1281" s="40">
-        <v>6763.4717461347855</v>
+        <v>6763.438455546866</v>
       </c>
       <c r="E1281" s="41">
-        <v>6314.8122943439066</v>
+        <v>6313.0644742178474</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58206,7 +58206,7 @@
       <c r="L1281" s="40"/>
       <c r="M1281" s="40"/>
       <c r="N1281" s="40">
-        <v>64980.667300000001</v>
+        <v>64980.386099999996</v>
       </c>
     </row>
     <row r="1282" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58214,16 +58214,16 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>60275.661099999998</v>
+        <v>60273.5383</v>
       </c>
       <c r="C1282" s="40">
         <v>10726.6477</v>
       </c>
       <c r="D1282" s="40">
-        <v>5619.2449669061098</v>
+        <v>5619.0470672398424</v>
       </c>
       <c r="E1282" s="41">
-        <v>6314.2955472357626</v>
+        <v>6312.7594387381259</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76963.001599999989</v>
+        <v>76960.878800000006</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58252,16 +58252,16 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>62409.701300000001</v>
+        <v>62409.485999999997</v>
       </c>
       <c r="C1283" s="40">
         <v>11163.6018</v>
       </c>
       <c r="D1283" s="40">
-        <v>5590.4628647718337</v>
+        <v>5590.4435788815035</v>
       </c>
       <c r="E1283" s="41">
-        <v>6031.7573890143849</v>
+        <v>6030.4674406361755</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58282,7 +58282,7 @@
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>71799.068700000003</v>
+        <v>71798.853399999993</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58290,16 +58290,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>39451.049299999999</v>
+        <v>39449.790200000003</v>
       </c>
       <c r="C1284" s="40">
         <v>6226.7978999999996</v>
       </c>
       <c r="D1284" s="40">
-        <v>6335.6880909849342</v>
+        <v>6335.4858843258753</v>
       </c>
       <c r="E1284" s="41">
-        <v>5949.0908153292949</v>
+        <v>5948.9974337002468</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58320,7 +58320,7 @@
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55863.105599999995</v>
+        <v>55861.8465</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62549.529699999999</v>
+        <v>62549.301500000001</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5906.7692424441129</v>
+        <v>5906.7476927258731</v>
       </c>
       <c r="E1285" s="41">
-        <v>5833.9353487727321</v>
+        <v>5833.8403823555391</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58358,7 +58358,7 @@
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80275.0288</v>
+        <v>80274.800600000002</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62178.531900000002</v>
+        <v>62177.072800000002</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6203.8874328832135</v>
+        <v>6203.7418506078411</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.24805204119</v>
+        <v>5860.1697520558855</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58396,7 +58396,7 @@
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69942.473299999998</v>
+        <v>69941.014200000005</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58404,22 +58404,22 @@
         <v>46207</v>
       </c>
       <c r="B1287" s="40">
-        <v>39049.002899999999</v>
+        <v>39048.774599999997</v>
       </c>
       <c r="C1287" s="40">
         <v>6111.1090999999997</v>
       </c>
       <c r="D1287" s="40">
-        <v>6389.8389410197242</v>
+        <v>6389.8015828256111</v>
       </c>
       <c r="E1287" s="41">
-        <v>6051.852192934035</v>
+        <v>6051.7611162899429</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41">
-        <v>6419.3350482258757</v>
+        <v>6419.3350482258738</v>
       </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
@@ -58428,7 +58428,7 @@
       <c r="L1287" s="40"/>
       <c r="M1287" s="40"/>
       <c r="N1287" s="40">
-        <v>43154.176200000002</v>
+        <v>43153.947899999999</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58436,16 +58436,16 @@
         <v>46214</v>
       </c>
       <c r="B1288" s="40">
-        <v>68436.545299999998</v>
+        <v>68436.088900000002</v>
       </c>
       <c r="C1288" s="40">
         <v>11480.580099999999</v>
       </c>
       <c r="D1288" s="40">
-        <v>5961.0703208281266</v>
+        <v>5961.0305667393941</v>
       </c>
       <c r="E1288" s="41">
-        <v>6090.3416681921635</v>
+        <v>6090.2832231705042</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58466,7 +58466,7 @@
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>77062.879199999996</v>
+        <v>77062.4228</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58483,7 +58483,7 @@
         <v>5759.8158164727938</v>
       </c>
       <c r="E1289" s="41">
-        <v>6048.2804215664191</v>
+        <v>6048.2260594239006</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58495,7 +58495,7 @@
         <v>8859.3817452840904</v>
       </c>
       <c r="I1289" s="41">
-        <v>6807.6707383696876</v>
+        <v>6807.6707383696894</v>
       </c>
       <c r="J1289" s="40">
         <v>5420.6954999999998</v>
@@ -58512,16 +58512,16 @@
         <v>46228</v>
       </c>
       <c r="B1290" s="40">
-        <v>79758.790599999993</v>
+        <v>79745.815300000002</v>
       </c>
       <c r="C1290" s="40">
         <v>13474.185299999999</v>
       </c>
       <c r="D1290" s="40">
-        <v>5919.3775968035707</v>
+        <v>5918.4146220699522</v>
       </c>
       <c r="E1290" s="41">
-        <v>6030.6724450011134</v>
+        <v>6030.3556099398693</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58542,7 +58542,7 @@
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86936.563399999999</v>
+        <v>86923.588099999994</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58559,7 +58559,7 @@
         <v>5729.4240404628799</v>
       </c>
       <c r="E1291" s="41">
-        <v>5929.9932188320608</v>
+        <v>5929.6906961770919</v>
       </c>
       <c r="F1291" s="40">
         <v>1001.2517</v>
@@ -58580,7 +58580,7 @@
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>71058.550300000003</v>
+        <v>71058.550299999988</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58597,7 +58597,7 @@
         <v>6399.802136951751</v>
       </c>
       <c r="E1292" s="41">
-        <v>5962.2494377471758</v>
+        <v>5961.9680494653785</v>
       </c>
       <c r="F1292" s="40">
         <v>278.08030000000002</v>
@@ -58635,7 +58635,7 @@
         <v>6332.1775899330314</v>
       </c>
       <c r="E1293" s="41">
-        <v>6093.2704740978625</v>
+        <v>6092.9903972335987</v>
       </c>
       <c r="F1293" s="40">
         <v>348.17270000000002</v>
@@ -58673,7 +58673,7 @@
         <v>5973.2487463122643</v>
       </c>
       <c r="E1294" s="41">
-        <v>6172.3827472487565</v>
+        <v>6172.3108796024108</v>
       </c>
       <c r="F1294" s="40">
         <v>922.0231</v>
@@ -58688,13 +58688,13 @@
         <v>5774.2266878472819</v>
       </c>
       <c r="J1294" s="40">
-        <v>11287.036599999999</v>
+        <v>11287.231299999999</v>
       </c>
       <c r="K1294" s="40"/>
       <c r="L1294" s="40"/>
       <c r="M1294" s="40"/>
       <c r="N1294" s="40">
-        <v>79999.687900000004</v>
+        <v>79999.882600000012</v>
       </c>
     </row>
     <row r="1295" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58702,16 +58702,16 @@
         <v>46263</v>
       </c>
       <c r="B1295" s="40">
-        <v>29494.129700000001</v>
+        <v>29505.966700000001</v>
       </c>
       <c r="C1295" s="40">
         <v>4617.8216000000002</v>
       </c>
       <c r="D1295" s="40">
-        <v>6387.0223353799556</v>
+        <v>6389.5856652409439</v>
       </c>
       <c r="E1295" s="41">
-        <v>6123.8757089057108</v>
+        <v>6124.1580031677713</v>
       </c>
       <c r="F1295" s="40">
         <v>1184.9033999999999</v>
@@ -58723,7 +58723,7 @@
         <v>8811.0926199410151</v>
       </c>
       <c r="I1295" s="41">
-        <v>6349.0005379130998</v>
+        <v>6349.0005379131017</v>
       </c>
       <c r="J1295" s="40">
         <v>5504.6995999999999</v>
@@ -58732,7 +58732,7 @@
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
       <c r="N1295" s="40">
-        <v>36183.7327</v>
+        <v>36195.5697</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58740,16 +58740,16 @@
         <v>46270</v>
       </c>
       <c r="B1296" s="40">
-        <v>67427.372399999993</v>
+        <v>67428.723299999998</v>
       </c>
       <c r="C1296" s="40">
         <v>11950.0612</v>
       </c>
       <c r="D1296" s="40">
-        <v>5642.4290446311679</v>
+        <v>5642.5420900773288</v>
       </c>
       <c r="E1296" s="41">
-        <v>6170.0984981317361</v>
+        <v>6170.4201679614616</v>
       </c>
       <c r="F1296" s="40">
         <v>113.3493</v>
@@ -58770,7 +58770,7 @@
       <c r="L1296" s="40"/>
       <c r="M1296" s="40"/>
       <c r="N1296" s="40">
-        <v>72960.542799999996</v>
+        <v>72961.893700000001</v>
       </c>
     </row>
     <row r="1297" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58778,16 +58778,16 @@
         <v>46277</v>
       </c>
       <c r="B1297" s="40">
-        <v>67477.834499999997</v>
+        <v>69685.927200000006</v>
       </c>
       <c r="C1297" s="40">
-        <v>11450.9987</v>
+        <v>11662.5969</v>
       </c>
       <c r="D1297" s="40">
-        <v>5892.7466737027926</v>
+        <v>5975.1638333654491</v>
       </c>
       <c r="E1297" s="41">
-        <v>6060.2459454268055</v>
+        <v>6082.4480262448069</v>
       </c>
       <c r="F1297" s="40">
         <v>231.03710000000001</v>
@@ -58802,13 +58802,13 @@
         <v>6415.0076095323757</v>
       </c>
       <c r="J1297" s="40">
-        <v>10406.3367</v>
+        <v>10138.6448</v>
       </c>
       <c r="K1297" s="40"/>
       <c r="L1297" s="40"/>
       <c r="M1297" s="40"/>
       <c r="N1297" s="40">
-        <v>78115.208299999998</v>
+        <v>80055.609100000001</v>
       </c>
     </row>
     <row r="1298" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58816,37 +58816,37 @@
         <v>46284</v>
       </c>
       <c r="B1298" s="40">
-        <v>39089.029199999997</v>
+        <v>44404.709300000002</v>
       </c>
       <c r="C1298" s="40">
-        <v>6147.1118999999999</v>
+        <v>7163.5258999999996</v>
       </c>
       <c r="D1298" s="40">
-        <v>6358.9259209678603</v>
+        <v>6198.7225173569914</v>
       </c>
       <c r="E1298" s="41">
-        <v>6021.1469873608876</v>
+        <v>6024.7231996219452</v>
       </c>
       <c r="F1298" s="40">
-        <v>1126.4794999999999</v>
+        <v>1127.9690000000001</v>
       </c>
       <c r="G1298" s="40">
         <v>172.87860000000001</v>
       </c>
       <c r="H1298" s="40">
-        <v>6516.0147062736505</v>
+        <v>6524.6305789149146</v>
       </c>
       <c r="I1298" s="41">
-        <v>6677.4760864342288</v>
+        <v>6680.7117003884478</v>
       </c>
       <c r="J1298" s="40">
-        <v>14531.437400000001</v>
+        <v>15213.141900000001</v>
       </c>
       <c r="K1298" s="40"/>
       <c r="L1298" s="40"/>
       <c r="M1298" s="40"/>
       <c r="N1298" s="40">
-        <v>54746.946100000001</v>
+        <v>60745.820200000002</v>
       </c>
     </row>
     <row r="1299" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58854,54 +58854,76 @@
         <v>46291</v>
       </c>
       <c r="B1299" s="40">
-        <v>50892.176399999997</v>
+        <v>67096.003200000006</v>
       </c>
       <c r="C1299" s="40">
-        <v>8088.1421</v>
+        <v>11138.780699999999</v>
       </c>
       <c r="D1299" s="40">
-        <v>6292.1961274641799</v>
+        <v>6023.639840579679</v>
       </c>
       <c r="E1299" s="41">
-        <v>6021.7477934114968</v>
+        <v>5977.9293171439294</v>
       </c>
       <c r="F1299" s="40">
-        <v>48.436999999999998</v>
+        <v>166.6345</v>
       </c>
       <c r="G1299" s="40">
-        <v>11.057</v>
+        <v>28.283300000000001</v>
       </c>
       <c r="H1299" s="40">
-        <v>4380.6638328660574</v>
+        <v>5891.621557597593</v>
       </c>
       <c r="I1299" s="41">
-        <v>6998.5017528971393</v>
+        <v>6995.9714458217259</v>
       </c>
       <c r="J1299" s="40">
-        <v>9331.2592000000004</v>
+        <v>12272.9889</v>
       </c>
       <c r="K1299" s="40"/>
       <c r="L1299" s="40"/>
       <c r="M1299" s="40"/>
       <c r="N1299" s="40">
-        <v>60271.872599999995</v>
+        <v>79535.626600000003</v>
       </c>
     </row>
     <row r="1300" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1300" s="39"/>
-      <c r="B1300" s="40"/>
-      <c r="C1300" s="40"/>
-      <c r="D1300" s="40"/>
-      <c r="E1300" s="41"/>
-      <c r="F1300" s="40"/>
-      <c r="G1300" s="40"/>
-      <c r="H1300" s="40"/>
-      <c r="I1300" s="41"/>
-      <c r="J1300" s="40"/>
+      <c r="A1300" s="39">
+        <v>46298</v>
+      </c>
+      <c r="B1300" s="40">
+        <v>23873.5465</v>
+      </c>
+      <c r="C1300" s="40">
+        <v>4094.9123</v>
+      </c>
+      <c r="D1300" s="40">
+        <v>5830.0507436996877</v>
+      </c>
+      <c r="E1300" s="41">
+        <v>6106.6406161927143</v>
+      </c>
+      <c r="F1300" s="40">
+        <v>253.57679999999999</v>
+      </c>
+      <c r="G1300" s="40">
+        <v>29.2044</v>
+      </c>
+      <c r="H1300" s="40">
+        <v>8682.8286148662519</v>
+      </c>
+      <c r="I1300" s="41">
+        <v>6491.0420638951573</v>
+      </c>
+      <c r="J1300" s="40">
+        <v>4517.7060000000001</v>
+      </c>
       <c r="K1300" s="40"/>
       <c r="L1300" s="40"/>
       <c r="M1300" s="40"/>
-      <c r="N1300" s="40"/>
+      <c r="N1300" s="40">
+        <v>28644.829300000001</v>
+      </c>
     </row>
     <row r="1301" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1301" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2DAEEE-1220-43BD-8FFA-A626A3BCCD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E64C24-CEF1-47CC-8011-F41DCA5CDAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55486,7 +55486,7 @@
         <v>4532.3036837254567</v>
       </c>
       <c r="E1210" s="36">
-        <v>4508.5895396139722</v>
+        <v>4508.5895396139713</v>
       </c>
       <c r="F1210" s="35">
         <v>1813.4111</v>
@@ -55726,7 +55726,7 @@
         <v>4337.7130954170489</v>
       </c>
       <c r="I1216" s="36">
-        <v>4764.4312599888553</v>
+        <v>4764.4312599888563</v>
       </c>
       <c r="J1216" s="35">
         <v>3920.1588999999999</v>
@@ -55752,7 +55752,7 @@
         <v>4774.6764373626611</v>
       </c>
       <c r="E1217" s="36">
-        <v>4705.8123550761284</v>
+        <v>4705.8123550761293</v>
       </c>
       <c r="F1217" s="35">
         <v>1657.8610000000001</v>
@@ -55790,7 +55790,7 @@
         <v>4728.8964531933216</v>
       </c>
       <c r="E1218" s="36">
-        <v>4735.8590672017517</v>
+        <v>4735.8590672017526</v>
       </c>
       <c r="F1218" s="35">
         <v>1098.2744</v>
@@ -55866,7 +55866,7 @@
         <v>4568.4292538250847</v>
       </c>
       <c r="E1220" s="36">
-        <v>4662.2080120947376</v>
+        <v>4662.2080120947385</v>
       </c>
       <c r="F1220" s="35">
         <v>779.47170000000006</v>
@@ -56398,7 +56398,7 @@
         <v>4897.6606435012372</v>
       </c>
       <c r="E1234" s="36">
-        <v>4765.8082224709979</v>
+        <v>4765.808222470997</v>
       </c>
       <c r="F1234" s="35">
         <v>556.48080000000004</v>
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6129.9007248539547</v>
+        <v>6129.9007248539556</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56905,7 +56905,7 @@
         <v>5760.8028278407392</v>
       </c>
       <c r="I1247" s="36">
-        <v>5388.6606709613816</v>
+        <v>5388.6606709613825</v>
       </c>
       <c r="J1247" s="35">
         <v>13767.5789</v>
@@ -57036,16 +57036,16 @@
         <v>45955</v>
       </c>
       <c r="B1251" s="35">
-        <v>54245.623500000002</v>
+        <v>54235.808199999999</v>
       </c>
       <c r="C1251" s="35">
         <v>9527.3052000000007</v>
       </c>
       <c r="D1251" s="35">
-        <v>5693.7006174631624</v>
+        <v>5692.6703891043608</v>
       </c>
       <c r="E1251" s="36">
-        <v>5005.7288484653054</v>
+        <v>5005.4562721568391</v>
       </c>
       <c r="F1251" s="35">
         <v>1154.2166999999999</v>
@@ -57066,7 +57066,7 @@
       <c r="L1251" s="35"/>
       <c r="M1251" s="35"/>
       <c r="N1251" s="37">
-        <v>60819.540999999997</v>
+        <v>60809.725699999995</v>
       </c>
     </row>
     <row r="1252" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57083,7 +57083,7 @@
         <v>4714.7055270892297</v>
       </c>
       <c r="E1252" s="36">
-        <v>4978.8868075822375</v>
+        <v>4978.6180087808279</v>
       </c>
       <c r="F1252" s="35">
         <v>979.83450000000005</v>
@@ -57121,7 +57121,7 @@
         <v>5679.5787797836083</v>
       </c>
       <c r="E1253" s="36">
-        <v>5193.2421766004063</v>
+        <v>5193.0461448605711</v>
       </c>
       <c r="F1253" s="35">
         <v>3024.5275999999999</v>
@@ -57159,7 +57159,7 @@
         <v>5045.5436514588309</v>
       </c>
       <c r="E1254" s="36">
-        <v>5296.9811686799094</v>
+        <v>5296.7670785997434</v>
       </c>
       <c r="F1254" s="35">
         <v>2122.2244000000001</v>
@@ -57188,16 +57188,16 @@
         <v>45983</v>
       </c>
       <c r="B1255" s="35">
-        <v>84371.745500000005</v>
+        <v>84371.3943</v>
       </c>
       <c r="C1255" s="35">
         <v>13591.8501</v>
       </c>
       <c r="D1255" s="35">
-        <v>6207.5247210090993</v>
+        <v>6207.4988819954688</v>
       </c>
       <c r="E1255" s="36">
-        <v>5572.0777245297722</v>
+        <v>5571.8930564519387</v>
       </c>
       <c r="F1255" s="35">
         <v>2745.8622</v>
@@ -57218,7 +57218,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99658.361500000014</v>
+        <v>99658.010300000009</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57235,7 +57235,7 @@
         <v>5185.5703229900746</v>
       </c>
       <c r="E1256" s="36">
-        <v>5466.6660097942377</v>
+        <v>5466.6600135995477</v>
       </c>
       <c r="F1256" s="35">
         <v>3139.7898</v>
@@ -57247,7 +57247,7 @@
         <v>7224.1319647365126</v>
       </c>
       <c r="I1256" s="36">
-        <v>6257.5010579608352</v>
+        <v>6257.5010579608343</v>
       </c>
       <c r="J1256" s="35">
         <v>9243.7037999999993</v>
@@ -57273,7 +57273,7 @@
         <v>5244.3681512482881</v>
       </c>
       <c r="E1257" s="36">
-        <v>5418.2025455518215</v>
+        <v>5418.196038308166</v>
       </c>
       <c r="F1257" s="35">
         <v>2948.9110000000001</v>
@@ -57285,7 +57285,7 @@
         <v>6414.561079819212</v>
       </c>
       <c r="I1257" s="36">
-        <v>6856.4662016578131</v>
+        <v>6856.4662016578122</v>
       </c>
       <c r="J1257" s="35">
         <v>7037.5686999999998</v>
@@ -57311,7 +57311,7 @@
         <v>4962.80776653056</v>
       </c>
       <c r="E1258" s="36">
-        <v>5447.1166811956527</v>
+        <v>5447.1101005891041</v>
       </c>
       <c r="F1258" s="35">
         <v>4360.9017999999996</v>
@@ -57399,7 +57399,7 @@
         <v>4873.0105884306095</v>
       </c>
       <c r="I1260" s="36">
-        <v>6633.6514180995455</v>
+        <v>6633.6514180995446</v>
       </c>
       <c r="J1260" s="35">
         <v>7680.5316000000003</v>
@@ -57437,7 +57437,7 @@
         <v>4523.51742353193</v>
       </c>
       <c r="I1261" s="36">
-        <v>6386.0309256033561</v>
+        <v>6386.030925603357</v>
       </c>
       <c r="J1261" s="35">
         <v>15412.583500000001</v>
@@ -57513,7 +57513,7 @@
         <v>7518.8883004544587</v>
       </c>
       <c r="I1263" s="36">
-        <v>6202.6386875506842</v>
+        <v>6202.638687550686</v>
       </c>
       <c r="J1263" s="35">
         <v>7841.0056000000004</v>
@@ -57568,16 +57568,16 @@
         <v>46053</v>
       </c>
       <c r="B1265" s="40">
-        <v>66533.447499999995</v>
+        <v>66432.8995</v>
       </c>
       <c r="C1265" s="40">
         <v>12751.894200000001</v>
       </c>
       <c r="D1265" s="40">
-        <v>5217.5344663697088</v>
+        <v>5209.6495201473672</v>
       </c>
       <c r="E1265" s="41">
-        <v>5316.3271849422181</v>
+        <v>5313.8214238511164</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57598,7 +57598,7 @@
       <c r="L1265" s="40"/>
       <c r="M1265" s="40"/>
       <c r="N1265" s="40">
-        <v>77712.414199999985</v>
+        <v>77611.866200000004</v>
       </c>
     </row>
     <row r="1266" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57615,7 +57615,7 @@
         <v>5371.3583018580512</v>
       </c>
       <c r="E1266" s="41">
-        <v>5320.2886080203034</v>
+        <v>5317.8898441781166</v>
       </c>
       <c r="F1266" s="40">
         <v>1799.4023999999999</v>
@@ -57653,7 +57653,7 @@
         <v>5718.2510112775044</v>
       </c>
       <c r="E1267" s="41">
-        <v>5387.993313828857</v>
+        <v>5385.9113060763166</v>
       </c>
       <c r="F1267" s="40">
         <v>1822.9809</v>
@@ -57691,7 +57691,7 @@
         <v>5134.2595581103988</v>
       </c>
       <c r="E1268" s="41">
-        <v>5333.4685564878391</v>
+        <v>5331.4931273620705</v>
       </c>
       <c r="F1268" s="40">
         <v>1326.8929000000001</v>
@@ -57729,7 +57729,7 @@
         <v>5300.0847228510156</v>
       </c>
       <c r="E1269" s="41">
-        <v>5319.0465830690327</v>
+        <v>5317.050309113537</v>
       </c>
       <c r="F1269" s="40">
         <v>1050.4068</v>
@@ -57872,16 +57872,16 @@
         <v>46109</v>
       </c>
       <c r="B1273" s="40">
-        <v>62466.066500000001</v>
+        <v>62465.657500000001</v>
       </c>
       <c r="C1273" s="40">
         <v>10894.957700000001</v>
       </c>
       <c r="D1273" s="40">
-        <v>5733.4840776848541</v>
+        <v>5733.4465373830681</v>
       </c>
       <c r="E1273" s="41">
-        <v>5668.761618787079</v>
+        <v>5668.7522645558811</v>
       </c>
       <c r="F1273" s="40">
         <v>700.99080000000004</v>
@@ -57902,7 +57902,7 @@
       <c r="L1273" s="40"/>
       <c r="M1273" s="40"/>
       <c r="N1273" s="40">
-        <v>74204.935100000002</v>
+        <v>74204.526100000003</v>
       </c>
     </row>
     <row r="1274" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57919,7 +57919,7 @@
         <v>5396.3988069518982</v>
       </c>
       <c r="E1274" s="41">
-        <v>5577.9970067451313</v>
+        <v>5577.9872534047008</v>
       </c>
       <c r="F1274" s="40">
         <v>1047.5085999999999</v>
@@ -57957,7 +57957,7 @@
         <v>6106.9845862172506</v>
       </c>
       <c r="E1275" s="41">
-        <v>5668.1234508569378</v>
+        <v>5668.112341349477</v>
       </c>
       <c r="F1275" s="40">
         <v>1448.9915000000001</v>
@@ -57995,7 +57995,7 @@
         <v>5803.5152098997523</v>
       </c>
       <c r="E1276" s="41">
-        <v>5696.558153105696</v>
+        <v>5696.5463667078575</v>
       </c>
       <c r="F1276" s="40">
         <v>283.16950000000003</v>
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62177.072800000002</v>
+        <v>62176.642</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6203.7418506078411</v>
+        <v>6203.6988673687001</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.1697520558855</v>
+        <v>5860.1602106778782</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58396,7 +58396,7 @@
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69941.014200000005</v>
+        <v>69940.583400000003</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58404,16 +58404,16 @@
         <v>46207</v>
       </c>
       <c r="B1287" s="40">
-        <v>39048.774599999997</v>
+        <v>39048.559200000003</v>
       </c>
       <c r="C1287" s="40">
         <v>6111.1090999999997</v>
       </c>
       <c r="D1287" s="40">
-        <v>6389.8015828256111</v>
+        <v>6389.766335541286</v>
       </c>
       <c r="E1287" s="41">
-        <v>6051.7611162899429</v>
+        <v>6051.7437553084064</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
@@ -58428,7 +58428,7 @@
       <c r="L1287" s="40"/>
       <c r="M1287" s="40"/>
       <c r="N1287" s="40">
-        <v>43153.947899999999</v>
+        <v>43153.732500000006</v>
       </c>
     </row>
     <row r="1288" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58445,7 +58445,7 @@
         <v>5961.0305667393941</v>
       </c>
       <c r="E1288" s="41">
-        <v>6090.2832231705042</v>
+        <v>6090.2673010908256</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58483,7 +58483,7 @@
         <v>5759.8158164727938</v>
       </c>
       <c r="E1289" s="41">
-        <v>6048.2260594239006</v>
+        <v>6048.2096731861475</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58521,7 +58521,7 @@
         <v>5918.4146220699522</v>
       </c>
       <c r="E1290" s="41">
-        <v>6030.3556099398693</v>
+        <v>6030.3506410817718</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58702,16 +58702,16 @@
         <v>46263</v>
       </c>
       <c r="B1295" s="40">
-        <v>29505.966700000001</v>
+        <v>29505.7251</v>
       </c>
       <c r="C1295" s="40">
         <v>4617.8216000000002</v>
       </c>
       <c r="D1295" s="40">
-        <v>6389.5856652409439</v>
+        <v>6389.5333461994287</v>
       </c>
       <c r="E1295" s="41">
-        <v>6124.1580031677713</v>
+        <v>6124.1522413789971</v>
       </c>
       <c r="F1295" s="40">
         <v>1184.9033999999999</v>
@@ -58732,7 +58732,7 @@
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
       <c r="N1295" s="40">
-        <v>36195.5697</v>
+        <v>36195.328100000006</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58749,7 +58749,7 @@
         <v>5642.5420900773288</v>
       </c>
       <c r="E1296" s="41">
-        <v>6170.4201679614616</v>
+        <v>6170.4142750269639</v>
       </c>
       <c r="F1296" s="40">
         <v>113.3493</v>
@@ -58787,7 +58787,7 @@
         <v>5975.1638333654491</v>
       </c>
       <c r="E1297" s="41">
-        <v>6082.4480262448069</v>
+        <v>6082.4423134165936</v>
       </c>
       <c r="F1297" s="40">
         <v>231.03710000000001</v>
@@ -58816,16 +58816,16 @@
         <v>46284</v>
       </c>
       <c r="B1298" s="40">
-        <v>44404.709300000002</v>
+        <v>43932.13</v>
       </c>
       <c r="C1298" s="40">
-        <v>7163.5258999999996</v>
+        <v>7079.0905000000002</v>
       </c>
       <c r="D1298" s="40">
-        <v>6198.7225173569914</v>
+        <v>6205.9003201046798</v>
       </c>
       <c r="E1298" s="41">
-        <v>6024.7231996219452</v>
+        <v>6025.6228901404429</v>
       </c>
       <c r="F1298" s="40">
         <v>1127.9690000000001</v>
@@ -58846,7 +58846,7 @@
       <c r="L1298" s="40"/>
       <c r="M1298" s="40"/>
       <c r="N1298" s="40">
-        <v>60745.820200000002</v>
+        <v>60273.240899999997</v>
       </c>
     </row>
     <row r="1299" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58854,37 +58854,37 @@
         <v>46291</v>
       </c>
       <c r="B1299" s="40">
-        <v>67096.003200000006</v>
+        <v>71543.516199999998</v>
       </c>
       <c r="C1299" s="40">
-        <v>11138.780699999999</v>
+        <v>12271.5756</v>
       </c>
       <c r="D1299" s="40">
-        <v>6023.639840579679</v>
+        <v>5830.0187793326231</v>
       </c>
       <c r="E1299" s="41">
-        <v>5977.9293171439294</v>
+        <v>5929.4070337481608</v>
       </c>
       <c r="F1299" s="40">
-        <v>166.6345</v>
+        <v>373.93790000000001</v>
       </c>
       <c r="G1299" s="40">
-        <v>28.283300000000001</v>
+        <v>50.912399999999998</v>
       </c>
       <c r="H1299" s="40">
-        <v>5891.621557597593</v>
+        <v>7344.7313424627409</v>
       </c>
       <c r="I1299" s="41">
-        <v>6995.9714458217259</v>
+        <v>7129.4720836251372</v>
       </c>
       <c r="J1299" s="40">
-        <v>12272.9889</v>
+        <v>12504.625</v>
       </c>
       <c r="K1299" s="40"/>
       <c r="L1299" s="40"/>
       <c r="M1299" s="40"/>
       <c r="N1299" s="40">
-        <v>79535.626600000003</v>
+        <v>84422.079100000003</v>
       </c>
     </row>
     <row r="1300" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58892,54 +58892,76 @@
         <v>46298</v>
       </c>
       <c r="B1300" s="40">
-        <v>23873.5465</v>
+        <v>28042.4519</v>
       </c>
       <c r="C1300" s="40">
-        <v>4094.9123</v>
+        <v>4748.5802000000003</v>
       </c>
       <c r="D1300" s="40">
-        <v>5830.0507436996877</v>
+        <v>5905.4392510839334</v>
       </c>
       <c r="E1300" s="41">
-        <v>6106.6406161927143</v>
+        <v>6049.0021696565937</v>
       </c>
       <c r="F1300" s="40">
-        <v>253.57679999999999</v>
+        <v>589.66489999999999</v>
       </c>
       <c r="G1300" s="40">
-        <v>29.2044</v>
+        <v>56.160499999999999</v>
       </c>
       <c r="H1300" s="40">
-        <v>8682.8286148662519</v>
+        <v>10499.637645676232</v>
       </c>
       <c r="I1300" s="41">
-        <v>6491.0420638951573</v>
+        <v>7146.7869866833389</v>
       </c>
       <c r="J1300" s="40">
-        <v>4517.7060000000001</v>
+        <v>4667.4883</v>
       </c>
       <c r="K1300" s="40"/>
       <c r="L1300" s="40"/>
       <c r="M1300" s="40"/>
       <c r="N1300" s="40">
-        <v>28644.829300000001</v>
+        <v>33299.605100000001</v>
       </c>
     </row>
     <row r="1301" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1301" s="39"/>
-      <c r="B1301" s="40"/>
-      <c r="C1301" s="40"/>
-      <c r="D1301" s="40"/>
-      <c r="E1301" s="41"/>
-      <c r="F1301" s="40"/>
-      <c r="G1301" s="40"/>
-      <c r="H1301" s="40"/>
-      <c r="I1301" s="41"/>
-      <c r="J1301" s="40"/>
+      <c r="A1301" s="39">
+        <v>46305</v>
+      </c>
+      <c r="B1301" s="40">
+        <v>34402.647299999997</v>
+      </c>
+      <c r="C1301" s="40">
+        <v>6035.0424999999996</v>
+      </c>
+      <c r="D1301" s="40">
+        <v>5700.4813636357985</v>
+      </c>
+      <c r="E1301" s="41">
+        <v>5943.0016097076223</v>
+      </c>
+      <c r="F1301" s="40">
+        <v>782.48879999999997</v>
+      </c>
+      <c r="G1301" s="40">
+        <v>116.3074</v>
+      </c>
+      <c r="H1301" s="40">
+        <v>6727.7645274505312</v>
+      </c>
+      <c r="I1301" s="41">
+        <v>7235.7434545526485</v>
+      </c>
+      <c r="J1301" s="40">
+        <v>5415.2542999999996</v>
+      </c>
       <c r="K1301" s="40"/>
       <c r="L1301" s="40"/>
       <c r="M1301" s="40"/>
-      <c r="N1301" s="40"/>
+      <c r="N1301" s="40">
+        <v>40600.390399999997</v>
+      </c>
     </row>
     <row r="1302" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1302" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E64C24-CEF1-47CC-8011-F41DCA5CDAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF9C95E-FE2D-4434-8B7C-0B21961BEC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164400000009</v>
+        <v>76699.164399999994</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.675999999999</v>
+        <v>62640.676000000007</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320599999992</v>
+        <v>68594.320600000006</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313499999997</v>
+        <v>52967.313500000004</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56343,7 +56343,7 @@
       <c r="L1232" s="35"/>
       <c r="M1232" s="35"/>
       <c r="N1232" s="37">
-        <v>68154.185600000012</v>
+        <v>68154.185599999997</v>
       </c>
     </row>
     <row r="1233" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56419,7 +56419,7 @@
       <c r="L1234" s="35"/>
       <c r="M1234" s="35"/>
       <c r="N1234" s="37">
-        <v>43632.772699999994</v>
+        <v>43632.772700000001</v>
       </c>
     </row>
     <row r="1235" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359399999994</v>
+        <v>53725.359400000001</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703700000005</v>
+        <v>57650.703699999998</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6129.9007248539556</v>
+        <v>6129.9007248539547</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639500000005</v>
+        <v>48636.639499999997</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57028,7 +57028,7 @@
       <c r="L1250" s="35"/>
       <c r="M1250" s="35"/>
       <c r="N1250" s="37">
-        <v>61868.669499999989</v>
+        <v>61868.669499999996</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57209,7 +57209,7 @@
         <v>7060.0167535971641</v>
       </c>
       <c r="I1255" s="36">
-        <v>5978.5241558371008</v>
+        <v>5978.5241558371017</v>
       </c>
       <c r="J1255" s="35">
         <v>12540.7538</v>
@@ -57218,7 +57218,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99658.010300000009</v>
+        <v>99658.010299999994</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.358000000007</v>
+        <v>78641.357999999993</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75388.57699999999</v>
+        <v>75388.577000000005</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.398179699102</v>
+        <v>6791.3981796990993</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92443.095499999996</v>
+        <v>92443.09550000001</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81329.603100000008</v>
+        <v>81329.603099999993</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57864,7 +57864,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>46083.950499999992</v>
+        <v>46083.950499999999</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57934,13 +57934,13 @@
         <v>6462.2132745375739</v>
       </c>
       <c r="J1274" s="40">
-        <v>8468.0509000000002</v>
+        <v>8611.5807000000004</v>
       </c>
       <c r="K1274" s="40"/>
       <c r="L1274" s="40"/>
       <c r="M1274" s="40"/>
       <c r="N1274" s="40">
-        <v>61514.844500000007</v>
+        <v>61658.374300000003</v>
       </c>
     </row>
     <row r="1275" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57960,16 +57960,16 @@
         <v>5668.112341349477</v>
       </c>
       <c r="F1275" s="40">
-        <v>1448.9915000000001</v>
+        <v>1445.7977000000001</v>
       </c>
       <c r="G1275" s="40">
         <v>226.815</v>
       </c>
       <c r="H1275" s="40">
-        <v>6388.4288957961335</v>
+        <v>6374.3478165024371</v>
       </c>
       <c r="I1275" s="41">
-        <v>5843.2818911670183</v>
+        <v>5838.9251014954116</v>
       </c>
       <c r="J1275" s="40">
         <v>3742.3887</v>
@@ -57978,7 +57978,7 @@
       <c r="L1275" s="40"/>
       <c r="M1275" s="40"/>
       <c r="N1275" s="40">
-        <v>30621.3825</v>
+        <v>30618.188699999999</v>
       </c>
     </row>
     <row r="1276" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58007,7 +58007,7 @@
         <v>4448.9160098100365</v>
       </c>
       <c r="I1276" s="41">
-        <v>5606.7869431513891</v>
+        <v>5601.9613587605481</v>
       </c>
       <c r="J1276" s="40">
         <v>6631.7284</v>
@@ -58016,7 +58016,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52467.279000000002</v>
+        <v>52467.278999999995</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58045,7 +58045,7 @@
         <v>5233.4920630608849</v>
       </c>
       <c r="I1277" s="41">
-        <v>5450.5130737709242</v>
+        <v>5445.9558109025565</v>
       </c>
       <c r="J1277" s="40">
         <v>5182.8711999999996</v>
@@ -58054,7 +58054,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37836.614700000006</v>
+        <v>37836.614699999998</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58083,7 +58083,7 @@
         <v>7577.0848344925953</v>
       </c>
       <c r="I1278" s="41">
-        <v>5643.0070838539059</v>
+        <v>5638.1343883262798</v>
       </c>
       <c r="J1278" s="40">
         <v>12650.7237</v>
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42470.174000000006</v>
+        <v>42470.173999999999</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58121,7 +58121,7 @@
         <v>7116.3687722704326</v>
       </c>
       <c r="I1279" s="41">
-        <v>6125.9423204335426</v>
+        <v>6120.2905213712966</v>
       </c>
       <c r="J1279" s="40">
         <v>4317.6605</v>
@@ -58214,16 +58214,16 @@
         <v>46172</v>
       </c>
       <c r="B1282" s="40">
-        <v>60273.5383</v>
+        <v>59737.818700000003</v>
       </c>
       <c r="C1282" s="40">
-        <v>10726.6477</v>
+        <v>10656.029399999999</v>
       </c>
       <c r="D1282" s="40">
-        <v>5619.0470672398424</v>
+        <v>5606.0110626196292</v>
       </c>
       <c r="E1282" s="41">
-        <v>6312.7594387381259</v>
+        <v>6310.1635077301444</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76960.878800000006</v>
+        <v>76425.159199999995</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58261,7 +58261,7 @@
         <v>5590.4435788815035</v>
       </c>
       <c r="E1283" s="41">
-        <v>6030.4674406361755</v>
+        <v>6027.8158332598769</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58290,16 +58290,16 @@
         <v>46186</v>
       </c>
       <c r="B1284" s="40">
-        <v>39449.790200000003</v>
+        <v>39384.790200000003</v>
       </c>
       <c r="C1284" s="40">
         <v>6226.7978999999996</v>
       </c>
       <c r="D1284" s="40">
-        <v>6335.4858843258753</v>
+        <v>6325.0471321704545</v>
       </c>
       <c r="E1284" s="41">
-        <v>5948.9974337002468</v>
+        <v>5944.6413788204418</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58320,7 +58320,7 @@
       <c r="L1284" s="40"/>
       <c r="M1284" s="40"/>
       <c r="N1284" s="40">
-        <v>55861.8465</v>
+        <v>55796.8465</v>
       </c>
     </row>
     <row r="1285" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58337,7 +58337,7 @@
         <v>5906.7476927258731</v>
       </c>
       <c r="E1285" s="41">
-        <v>5833.8403823555391</v>
+        <v>5829.1465483896136</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58375,7 +58375,7 @@
         <v>6203.6988673687001</v>
       </c>
       <c r="E1286" s="41">
-        <v>5860.1602106778782</v>
+        <v>5856.0145881332983</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58390,13 +58390,13 @@
         <v>6928.2649857850765</v>
       </c>
       <c r="J1286" s="40">
-        <v>7563.9697999999999</v>
+        <v>7553.0794999999998</v>
       </c>
       <c r="K1286" s="40"/>
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69940.583400000003</v>
+        <v>69929.693100000004</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58413,7 +58413,7 @@
         <v>6389.766335541286</v>
       </c>
       <c r="E1287" s="41">
-        <v>6051.7437553084064</v>
+        <v>6049.9974479733282</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
@@ -58536,13 +58536,13 @@
         <v>7167.4362558614857</v>
       </c>
       <c r="J1290" s="40">
-        <v>6905.1966000000002</v>
+        <v>6913.7996000000003</v>
       </c>
       <c r="K1290" s="40"/>
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86923.588099999994</v>
+        <v>86932.191099999996</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58550,16 +58550,16 @@
         <v>46235</v>
       </c>
       <c r="B1291" s="40">
-        <v>57773.6322</v>
+        <v>57591.279399999999</v>
       </c>
       <c r="C1291" s="40">
-        <v>10083.671899999999</v>
+        <v>10045.9069</v>
       </c>
       <c r="D1291" s="40">
-        <v>5729.4240404628799</v>
+        <v>5732.8103846950844</v>
       </c>
       <c r="E1291" s="41">
-        <v>5929.6906961770919</v>
+        <v>5930.6280456342411</v>
       </c>
       <c r="F1291" s="40">
         <v>1001.2517</v>
@@ -58580,7 +58580,7 @@
       <c r="L1291" s="40"/>
       <c r="M1291" s="40"/>
       <c r="N1291" s="40">
-        <v>71058.550299999988</v>
+        <v>70876.197499999995</v>
       </c>
     </row>
     <row r="1292" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58588,16 +58588,16 @@
         <v>46242</v>
       </c>
       <c r="B1292" s="40">
-        <v>55630.779900000001</v>
+        <v>55502.856500000002</v>
       </c>
       <c r="C1292" s="40">
-        <v>8692.5781000000006</v>
+        <v>8665.9781000000003</v>
       </c>
       <c r="D1292" s="40">
-        <v>6399.802136951751</v>
+        <v>6404.6846021916435</v>
       </c>
       <c r="E1292" s="41">
-        <v>5961.9680494653785</v>
+        <v>5963.5092057341508</v>
       </c>
       <c r="F1292" s="40">
         <v>278.08030000000002</v>
@@ -58618,7 +58618,7 @@
       <c r="L1292" s="40"/>
       <c r="M1292" s="40"/>
       <c r="N1292" s="40">
-        <v>60645.7402</v>
+        <v>60517.816800000001</v>
       </c>
     </row>
     <row r="1293" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58635,7 +58635,7 @@
         <v>6332.1775899330314</v>
       </c>
       <c r="E1293" s="41">
-        <v>6092.9903972335987</v>
+        <v>6094.7606810667921</v>
       </c>
       <c r="F1293" s="40">
         <v>348.17270000000002</v>
@@ -58673,7 +58673,7 @@
         <v>5973.2487463122643</v>
       </c>
       <c r="E1294" s="41">
-        <v>6172.3108796024108</v>
+        <v>6174.1647332135553</v>
       </c>
       <c r="F1294" s="40">
         <v>922.0231</v>
@@ -58711,7 +58711,7 @@
         <v>6389.5333461994287</v>
       </c>
       <c r="E1295" s="41">
-        <v>6124.1522413789971</v>
+        <v>6126.1563196167854</v>
       </c>
       <c r="F1295" s="40">
         <v>1184.9033999999999</v>
@@ -58732,7 +58732,7 @@
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
       <c r="N1295" s="40">
-        <v>36195.328100000006</v>
+        <v>36195.328099999999</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58854,37 +58854,37 @@
         <v>46291</v>
       </c>
       <c r="B1299" s="40">
-        <v>71543.516199999998</v>
+        <v>75643.767900000006</v>
       </c>
       <c r="C1299" s="40">
-        <v>12271.5756</v>
+        <v>12812.3523</v>
       </c>
       <c r="D1299" s="40">
-        <v>5830.0187793326231</v>
+        <v>5903.9718959335833</v>
       </c>
       <c r="E1299" s="41">
-        <v>5929.4070337481608</v>
+        <v>5948.1115181185096</v>
       </c>
       <c r="F1299" s="40">
-        <v>373.93790000000001</v>
+        <v>358.91109999999998</v>
       </c>
       <c r="G1299" s="40">
-        <v>50.912399999999998</v>
+        <v>49.597000000000001</v>
       </c>
       <c r="H1299" s="40">
-        <v>7344.7313424627409</v>
+        <v>7236.5485815674328</v>
       </c>
       <c r="I1299" s="41">
-        <v>7129.4720836251372</v>
+        <v>7114.0239613450467</v>
       </c>
       <c r="J1299" s="40">
-        <v>12504.625</v>
+        <v>12793.499100000001</v>
       </c>
       <c r="K1299" s="40"/>
       <c r="L1299" s="40"/>
       <c r="M1299" s="40"/>
       <c r="N1299" s="40">
-        <v>84422.079100000003</v>
+        <v>88796.178100000005</v>
       </c>
     </row>
     <row r="1300" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58892,37 +58892,37 @@
         <v>46298</v>
       </c>
       <c r="B1300" s="40">
-        <v>28042.4519</v>
+        <v>30790.842700000001</v>
       </c>
       <c r="C1300" s="40">
-        <v>4748.5802000000003</v>
+        <v>5265.8535000000002</v>
       </c>
       <c r="D1300" s="40">
-        <v>5905.4392510839334</v>
+        <v>5847.2653483428658</v>
       </c>
       <c r="E1300" s="41">
-        <v>6049.0021696565937</v>
+        <v>6060.1889585508006</v>
       </c>
       <c r="F1300" s="40">
-        <v>589.66489999999999</v>
+        <v>604.69169999999997</v>
       </c>
       <c r="G1300" s="40">
-        <v>56.160499999999999</v>
+        <v>57.475900000000003</v>
       </c>
       <c r="H1300" s="40">
-        <v>10499.637645676232</v>
+        <v>10520.786973322731</v>
       </c>
       <c r="I1300" s="41">
         <v>7146.7869866833389</v>
       </c>
       <c r="J1300" s="40">
-        <v>4667.4883</v>
+        <v>4604.3046999999997</v>
       </c>
       <c r="K1300" s="40"/>
       <c r="L1300" s="40"/>
       <c r="M1300" s="40"/>
       <c r="N1300" s="40">
-        <v>33299.605100000001</v>
+        <v>35999.839099999997</v>
       </c>
     </row>
     <row r="1301" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58930,54 +58930,76 @@
         <v>46305</v>
       </c>
       <c r="B1301" s="40">
-        <v>34402.647299999997</v>
+        <v>46833.122000000003</v>
       </c>
       <c r="C1301" s="40">
-        <v>6035.0424999999996</v>
+        <v>8556.9856</v>
       </c>
       <c r="D1301" s="40">
-        <v>5700.4813636357985</v>
+        <v>5473.086456987844</v>
       </c>
       <c r="E1301" s="41">
-        <v>5943.0016097076223</v>
+        <v>5893.0250562346109</v>
       </c>
       <c r="F1301" s="40">
-        <v>782.48879999999997</v>
+        <v>1017.8108999999999</v>
       </c>
       <c r="G1301" s="40">
-        <v>116.3074</v>
+        <v>157.3793</v>
       </c>
       <c r="H1301" s="40">
-        <v>6727.7645274505312</v>
+        <v>6467.2475986359068</v>
       </c>
       <c r="I1301" s="41">
-        <v>7235.7434545526485</v>
+        <v>7099.9597677194879</v>
       </c>
       <c r="J1301" s="40">
-        <v>5415.2542999999996</v>
+        <v>6030.6569</v>
       </c>
       <c r="K1301" s="40"/>
       <c r="L1301" s="40"/>
       <c r="M1301" s="40"/>
       <c r="N1301" s="40">
-        <v>40600.390399999997</v>
+        <v>53881.589800000002</v>
       </c>
     </row>
     <row r="1302" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1302" s="39"/>
-      <c r="B1302" s="40"/>
-      <c r="C1302" s="40"/>
-      <c r="D1302" s="40"/>
-      <c r="E1302" s="41"/>
-      <c r="F1302" s="40"/>
-      <c r="G1302" s="40"/>
-      <c r="H1302" s="40"/>
-      <c r="I1302" s="41"/>
-      <c r="J1302" s="40"/>
+      <c r="A1302" s="39">
+        <v>46312</v>
+      </c>
+      <c r="B1302" s="40">
+        <v>26327.8783</v>
+      </c>
+      <c r="C1302" s="40">
+        <v>3539.2494000000002</v>
+      </c>
+      <c r="D1302" s="40">
+        <v>7438.8310414066891</v>
+      </c>
+      <c r="E1302" s="41">
+        <v>5971.5395754024476</v>
+      </c>
+      <c r="F1302" s="40">
+        <v>361.16469999999998</v>
+      </c>
+      <c r="G1302" s="40">
+        <v>52.304699999999997</v>
+      </c>
+      <c r="H1302" s="40">
+        <v>6905.0142721399789</v>
+      </c>
+      <c r="I1302" s="41">
+        <v>6843.8516060566944</v>
+      </c>
+      <c r="J1302" s="40">
+        <v>2177.6768000000002</v>
+      </c>
       <c r="K1302" s="40"/>
       <c r="L1302" s="40"/>
       <c r="M1302" s="40"/>
-      <c r="N1302" s="40"/>
+      <c r="N1302" s="40">
+        <v>28866.719799999999</v>
+      </c>
     </row>
     <row r="1303" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="39"/>

--- a/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
+++ b/data_raw/serie_semanal_ingreso_medio_exportacion_inac.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\inac.local\archivos\GIF\Datos y Estadísticas\Publicaciones Web\Públicos\Boletín Semanal\Salidas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF9C95E-FE2D-4434-8B7C-0B21961BEC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B67970-4565-417B-A6DF-57314163C79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INAC" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -926,7 +926,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="21">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="22"/>
@@ -55659,7 +55659,7 @@
       <c r="L1214" s="35"/>
       <c r="M1214" s="35"/>
       <c r="N1214" s="37">
-        <v>76699.164399999994</v>
+        <v>76699.164400000009</v>
       </c>
     </row>
     <row r="1215" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55849,7 +55849,7 @@
       <c r="L1219" s="35"/>
       <c r="M1219" s="35"/>
       <c r="N1219" s="37">
-        <v>62640.676000000007</v>
+        <v>62640.675999999999</v>
       </c>
     </row>
     <row r="1220" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55925,7 +55925,7 @@
       <c r="L1221" s="35"/>
       <c r="M1221" s="35"/>
       <c r="N1221" s="37">
-        <v>68594.320600000006</v>
+        <v>68594.320599999992</v>
       </c>
     </row>
     <row r="1222" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -55963,7 +55963,7 @@
       <c r="L1222" s="35"/>
       <c r="M1222" s="35"/>
       <c r="N1222" s="37">
-        <v>52967.313500000004</v>
+        <v>52967.313499999997</v>
       </c>
     </row>
     <row r="1223" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56161,16 +56161,16 @@
         <v>45794</v>
       </c>
       <c r="B1228" s="35">
-        <v>74694.599300000002</v>
+        <v>74690.560599999997</v>
       </c>
       <c r="C1228" s="35">
         <v>14436.996499999999</v>
       </c>
       <c r="D1228" s="35">
-        <v>5173.8323341700607</v>
+        <v>5173.5525876175143</v>
       </c>
       <c r="E1228" s="36">
-        <v>5047.8023284131623</v>
+        <v>5047.723872666862</v>
       </c>
       <c r="F1228" s="35">
         <v>677.62339999999995</v>
@@ -56191,7 +56191,7 @@
       <c r="L1228" s="35"/>
       <c r="M1228" s="35"/>
       <c r="N1228" s="37">
-        <v>80235.211200000005</v>
+        <v>80231.172500000001</v>
       </c>
     </row>
     <row r="1229" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56208,7 +56208,7 @@
         <v>5125.7053923778949</v>
       </c>
       <c r="E1229" s="36">
-        <v>4982.9059091645086</v>
+        <v>4982.8298285873352</v>
       </c>
       <c r="F1229" s="35">
         <v>465.10070000000002</v>
@@ -56246,7 +56246,7 @@
         <v>5223.0643969288667</v>
       </c>
       <c r="E1230" s="36">
-        <v>5027.8916316333225</v>
+        <v>5027.8130969662652</v>
       </c>
       <c r="F1230" s="35">
         <v>186.41309999999999</v>
@@ -56284,7 +56284,7 @@
         <v>4742.1060383005579</v>
       </c>
       <c r="E1231" s="36">
-        <v>4960.8711832545605</v>
+        <v>4960.8000900175193</v>
       </c>
       <c r="F1231" s="35">
         <v>1023.9116</v>
@@ -56343,7 +56343,7 @@
       <c r="L1232" s="35"/>
       <c r="M1232" s="35"/>
       <c r="N1232" s="37">
-        <v>68154.185599999997</v>
+        <v>68154.185600000012</v>
       </c>
     </row>
     <row r="1233" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56419,7 +56419,7 @@
       <c r="L1234" s="35"/>
       <c r="M1234" s="35"/>
       <c r="N1234" s="37">
-        <v>43632.772700000001</v>
+        <v>43632.772699999994</v>
       </c>
     </row>
     <row r="1235" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56571,7 +56571,7 @@
       <c r="L1238" s="35"/>
       <c r="M1238" s="35"/>
       <c r="N1238" s="37">
-        <v>53725.359400000001</v>
+        <v>53725.359399999994</v>
       </c>
     </row>
     <row r="1239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56800,7 +56800,7 @@
       <c r="L1244" s="35"/>
       <c r="M1244" s="35"/>
       <c r="N1244" s="37">
-        <v>57650.703699999998</v>
+        <v>57650.703700000005</v>
       </c>
     </row>
     <row r="1245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -56829,7 +56829,7 @@
         <v>6180.9293021255098</v>
       </c>
       <c r="I1245" s="36">
-        <v>6129.9007248539547</v>
+        <v>6129.9007248539556</v>
       </c>
       <c r="J1245" s="35">
         <v>4208.4350999999997</v>
@@ -56838,7 +56838,7 @@
       <c r="L1245" s="35"/>
       <c r="M1245" s="35"/>
       <c r="N1245" s="37">
-        <v>48636.639499999997</v>
+        <v>48636.639500000005</v>
       </c>
     </row>
     <row r="1246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57028,7 +57028,7 @@
       <c r="L1250" s="35"/>
       <c r="M1250" s="35"/>
       <c r="N1250" s="37">
-        <v>61868.669499999996</v>
+        <v>61868.669499999989</v>
       </c>
     </row>
     <row r="1251" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57218,7 +57218,7 @@
       <c r="L1255" s="35"/>
       <c r="M1255" s="35"/>
       <c r="N1255" s="37">
-        <v>99658.010299999994</v>
+        <v>99658.010300000009</v>
       </c>
     </row>
     <row r="1256" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57294,7 +57294,7 @@
       <c r="L1257" s="35"/>
       <c r="M1257" s="35"/>
       <c r="N1257" s="37">
-        <v>78641.357999999993</v>
+        <v>78641.358000000007</v>
       </c>
     </row>
     <row r="1258" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57332,7 +57332,7 @@
       <c r="L1258" s="35"/>
       <c r="M1258" s="35"/>
       <c r="N1258" s="37">
-        <v>75388.577000000005</v>
+        <v>75388.57699999999</v>
       </c>
     </row>
     <row r="1259" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57577,7 +57577,7 @@
         <v>5209.6495201473672</v>
       </c>
       <c r="E1265" s="41">
-        <v>5313.8214238511164</v>
+        <v>5313.8214238511173</v>
       </c>
       <c r="F1265" s="40">
         <v>2790.8292999999999</v>
@@ -57589,7 +57589,7 @@
         <v>6118.476605644777</v>
       </c>
       <c r="I1265" s="41">
-        <v>6791.3981796990993</v>
+        <v>6791.3981796991011</v>
       </c>
       <c r="J1265" s="40">
         <v>8388.1373999999996</v>
@@ -57674,7 +57674,7 @@
       <c r="L1267" s="40"/>
       <c r="M1267" s="40"/>
       <c r="N1267" s="40">
-        <v>92443.09550000001</v>
+        <v>92443.095499999996</v>
       </c>
     </row>
     <row r="1268" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57712,7 +57712,7 @@
       <c r="L1268" s="40"/>
       <c r="M1268" s="40"/>
       <c r="N1268" s="40">
-        <v>81329.603099999993</v>
+        <v>81329.603100000008</v>
       </c>
     </row>
     <row r="1269" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -57817,7 +57817,7 @@
         <v>7025.7066080085497</v>
       </c>
       <c r="I1271" s="41">
-        <v>7474.9950981706661</v>
+        <v>7474.9950981706652</v>
       </c>
       <c r="J1271" s="40">
         <v>9744.1470000000008</v>
@@ -57864,7 +57864,7 @@
       <c r="L1272" s="40"/>
       <c r="M1272" s="40"/>
       <c r="N1272" s="40">
-        <v>46083.950499999999</v>
+        <v>46083.950499999992</v>
       </c>
     </row>
     <row r="1273" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58016,7 +58016,7 @@
       <c r="L1276" s="40"/>
       <c r="M1276" s="40"/>
       <c r="N1276" s="40">
-        <v>52467.278999999995</v>
+        <v>52467.279000000002</v>
       </c>
     </row>
     <row r="1277" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58054,7 +58054,7 @@
       <c r="L1277" s="40"/>
       <c r="M1277" s="40"/>
       <c r="N1277" s="40">
-        <v>37836.614699999998</v>
+        <v>37836.614700000006</v>
       </c>
     </row>
     <row r="1278" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58092,7 +58092,7 @@
       <c r="L1278" s="40"/>
       <c r="M1278" s="40"/>
       <c r="N1278" s="40">
-        <v>42470.173999999999</v>
+        <v>42470.174000000006</v>
       </c>
     </row>
     <row r="1279" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58100,16 +58100,16 @@
         <v>46151</v>
       </c>
       <c r="B1279" s="40">
-        <v>33626.428399999997</v>
+        <v>33626.1633</v>
       </c>
       <c r="C1279" s="40">
         <v>5126.8805000000002</v>
       </c>
       <c r="D1279" s="40">
-        <v>6558.8477047592578</v>
+        <v>6558.7959969029889</v>
       </c>
       <c r="E1279" s="41">
-        <v>5769.5812555643333</v>
+        <v>5769.5711665327963</v>
       </c>
       <c r="F1279" s="40">
         <v>968.41610000000003</v>
@@ -58130,7 +58130,7 @@
       <c r="L1279" s="40"/>
       <c r="M1279" s="40"/>
       <c r="N1279" s="40">
-        <v>38912.504999999997</v>
+        <v>38912.2399</v>
       </c>
     </row>
     <row r="1280" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58147,7 +58147,7 @@
         <v>6534.2709261660411</v>
       </c>
       <c r="E1280" s="41">
-        <v>6014.1896418591386</v>
+        <v>6014.180260152566</v>
       </c>
       <c r="F1280" s="40">
         <v>105.7779</v>
@@ -58185,7 +58185,7 @@
         <v>6763.438455546866</v>
       </c>
       <c r="E1281" s="41">
-        <v>6313.0644742178474</v>
+        <v>6313.055488649622</v>
       </c>
       <c r="F1281" s="40">
         <v>2628.1927000000001</v>
@@ -58223,7 +58223,7 @@
         <v>5606.0110626196292</v>
       </c>
       <c r="E1282" s="41">
-        <v>6310.1635077301444</v>
+        <v>6310.1558547457089</v>
       </c>
       <c r="F1282" s="40">
         <v>1610.2809999999999</v>
@@ -58244,7 +58244,7 @@
       <c r="L1282" s="40"/>
       <c r="M1282" s="40"/>
       <c r="N1282" s="40">
-        <v>76425.159199999995</v>
+        <v>76425.159200000009</v>
       </c>
     </row>
     <row r="1283" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58252,16 +58252,16 @@
         <v>46179</v>
       </c>
       <c r="B1283" s="40">
-        <v>62409.485999999997</v>
+        <v>62409.2016</v>
       </c>
       <c r="C1283" s="40">
         <v>11163.6018</v>
       </c>
       <c r="D1283" s="40">
-        <v>5590.4435788815035</v>
+        <v>5590.4181032325969</v>
       </c>
       <c r="E1283" s="41">
-        <v>6027.8158332598769</v>
+        <v>6027.8089688031914</v>
       </c>
       <c r="F1283" s="40">
         <v>1884.8083999999999</v>
@@ -58282,7 +58282,7 @@
       <c r="L1283" s="40"/>
       <c r="M1283" s="40"/>
       <c r="N1283" s="40">
-        <v>71798.853399999993</v>
+        <v>71798.568999999989</v>
       </c>
     </row>
     <row r="1284" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58299,7 +58299,7 @@
         <v>6325.0471321704545</v>
       </c>
       <c r="E1284" s="41">
-        <v>5944.6413788204418</v>
+        <v>5944.6345195567283</v>
       </c>
       <c r="F1284" s="40">
         <v>1015.2809</v>
@@ -58328,16 +58328,16 @@
         <v>46193</v>
       </c>
       <c r="B1285" s="40">
-        <v>62549.301500000001</v>
+        <v>62547.472300000001</v>
       </c>
       <c r="C1285" s="40">
         <v>10589.4656</v>
       </c>
       <c r="D1285" s="40">
-        <v>5906.7476927258731</v>
+        <v>5906.5749550194496</v>
       </c>
       <c r="E1285" s="41">
-        <v>5829.1465483896136</v>
+        <v>5829.0939856446903</v>
       </c>
       <c r="F1285" s="40">
         <v>600.94730000000004</v>
@@ -58358,7 +58358,7 @@
       <c r="L1285" s="40"/>
       <c r="M1285" s="40"/>
       <c r="N1285" s="40">
-        <v>80274.800600000002</v>
+        <v>80272.971400000009</v>
       </c>
     </row>
     <row r="1286" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58366,16 +58366,16 @@
         <v>46200</v>
       </c>
       <c r="B1286" s="40">
-        <v>62176.642</v>
+        <v>62175.957300000002</v>
       </c>
       <c r="C1286" s="40">
         <v>10022.5113</v>
       </c>
       <c r="D1286" s="40">
-        <v>6203.6988673687001</v>
+        <v>6203.6305511573737</v>
       </c>
       <c r="E1286" s="41">
-        <v>5856.0145881332983</v>
+        <v>5855.9525141703016</v>
       </c>
       <c r="F1286" s="40">
         <v>199.9716</v>
@@ -58396,7 +58396,7 @@
       <c r="L1286" s="40"/>
       <c r="M1286" s="40"/>
       <c r="N1286" s="40">
-        <v>69929.693100000004</v>
+        <v>69929.008400000006</v>
       </c>
     </row>
     <row r="1287" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58413,13 +58413,13 @@
         <v>6389.766335541286</v>
       </c>
       <c r="E1287" s="41">
-        <v>6049.9974479733282</v>
+        <v>6049.9222680992389</v>
       </c>
       <c r="F1287" s="40"/>
       <c r="G1287" s="40"/>
       <c r="H1287" s="40"/>
       <c r="I1287" s="41">
-        <v>6419.3350482258738</v>
+        <v>6419.3350482258757</v>
       </c>
       <c r="J1287" s="40">
         <v>4105.1733000000004</v>
@@ -58436,16 +58436,16 @@
         <v>46214</v>
       </c>
       <c r="B1288" s="40">
-        <v>68436.088900000002</v>
+        <v>68435.632400000002</v>
       </c>
       <c r="C1288" s="40">
         <v>11480.580099999999</v>
       </c>
       <c r="D1288" s="40">
-        <v>5961.0305667393941</v>
+        <v>5960.9908039402999</v>
       </c>
       <c r="E1288" s="41">
-        <v>6090.2673010908256</v>
+        <v>6090.1941117601627</v>
       </c>
       <c r="F1288" s="40">
         <v>420.85899999999998</v>
@@ -58466,7 +58466,7 @@
       <c r="L1288" s="40"/>
       <c r="M1288" s="40"/>
       <c r="N1288" s="40">
-        <v>77062.4228</v>
+        <v>77061.9663</v>
       </c>
     </row>
     <row r="1289" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58483,7 +58483,7 @@
         <v>5759.8158164727938</v>
       </c>
       <c r="E1289" s="41">
-        <v>6048.2096731861475</v>
+        <v>6048.1807348164111</v>
       </c>
       <c r="F1289" s="40">
         <v>506.89749999999998</v>
@@ -58495,7 +58495,7 @@
         <v>8859.3817452840904</v>
       </c>
       <c r="I1289" s="41">
-        <v>6807.6707383696894</v>
+        <v>6807.6707383696876</v>
       </c>
       <c r="J1289" s="40">
         <v>5420.6954999999998</v>
@@ -58521,7 +58521,7 @@
         <v>5918.4146220699522</v>
       </c>
       <c r="E1290" s="41">
-        <v>6030.3506410817718</v>
+        <v>6030.3401105166786</v>
       </c>
       <c r="F1290" s="40">
         <v>272.57619999999997</v>
@@ -58536,13 +58536,13 @@
         <v>7167.4362558614857</v>
       </c>
       <c r="J1290" s="40">
-        <v>6913.7996000000003</v>
+        <v>6913.7995000000001</v>
       </c>
       <c r="K1290" s="40"/>
       <c r="L1290" s="40"/>
       <c r="M1290" s="40"/>
       <c r="N1290" s="40">
-        <v>86932.191099999996</v>
+        <v>86932.190999999992</v>
       </c>
     </row>
     <row r="1291" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58559,7 +58559,7 @@
         <v>5732.8103846950844</v>
       </c>
       <c r="E1291" s="41">
-        <v>5930.6280456342411</v>
+        <v>5930.6177551156343</v>
       </c>
       <c r="F1291" s="40">
         <v>1001.2517</v>
@@ -58723,7 +58723,7 @@
         <v>8811.0926199410151</v>
       </c>
       <c r="I1295" s="41">
-        <v>6349.0005379131017</v>
+        <v>6349.0005379130998</v>
       </c>
       <c r="J1295" s="40">
         <v>5504.6995999999999</v>
@@ -58732,7 +58732,7 @@
       <c r="L1295" s="40"/>
       <c r="M1295" s="40"/>
       <c r="N1295" s="40">
-        <v>36195.328099999999</v>
+        <v>36195.328100000006</v>
       </c>
     </row>
     <row r="1296" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58778,16 +58778,16 @@
         <v>46277</v>
       </c>
       <c r="B1297" s="40">
-        <v>69685.927200000006</v>
+        <v>69809.735499999995</v>
       </c>
       <c r="C1297" s="40">
-        <v>11662.5969</v>
+        <v>11687.7719</v>
       </c>
       <c r="D1297" s="40">
-        <v>5975.1638333654491</v>
+        <v>5972.8865430715668</v>
       </c>
       <c r="E1297" s="41">
-        <v>6082.4423134165936</v>
+        <v>6081.749497183825</v>
       </c>
       <c r="F1297" s="40">
         <v>231.03710000000001</v>
@@ -58808,7 +58808,7 @@
       <c r="L1297" s="40"/>
       <c r="M1297" s="40"/>
       <c r="N1297" s="40">
-        <v>80055.609100000001</v>
+        <v>80179.417399999991</v>
       </c>
     </row>
     <row r="1298" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58825,7 +58825,7 @@
         <v>6205.9003201046798</v>
       </c>
       <c r="E1298" s="41">
-        <v>6025.6228901404429</v>
+        <v>6024.924052032934</v>
       </c>
       <c r="F1298" s="40">
         <v>1127.9690000000001</v>
@@ -58854,16 +58854,16 @@
         <v>46291</v>
       </c>
       <c r="B1299" s="40">
-        <v>75643.767900000006</v>
+        <v>75539.7402</v>
       </c>
       <c r="C1299" s="40">
-        <v>12812.3523</v>
+        <v>12784.3061</v>
       </c>
       <c r="D1299" s="40">
-        <v>5903.9718959335833</v>
+        <v>5908.7868836307043</v>
       </c>
       <c r="E1299" s="41">
-        <v>5948.1115181185096</v>
+        <v>5948.8829350216101</v>
       </c>
       <c r="F1299" s="40">
         <v>358.91109999999998</v>
@@ -58884,7 +58884,7 @@
       <c r="L1299" s="40"/>
       <c r="M1299" s="40"/>
       <c r="N1299" s="40">
-        <v>88796.178100000005</v>
+        <v>88692.150399999999</v>
       </c>
     </row>
     <row r="1300" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58892,37 +58892,37 @@
         <v>46298</v>
       </c>
       <c r="B1300" s="40">
-        <v>30790.842700000001</v>
+        <v>30491.8848</v>
       </c>
       <c r="C1300" s="40">
-        <v>5265.8535000000002</v>
+        <v>5251.6737000000003</v>
       </c>
       <c r="D1300" s="40">
-        <v>5847.2653483428658</v>
+        <v>5806.127063834906</v>
       </c>
       <c r="E1300" s="41">
-        <v>6060.1889585508006</v>
+        <v>6055.8010060226989</v>
       </c>
       <c r="F1300" s="40">
-        <v>604.69169999999997</v>
+        <v>605.98860000000002</v>
       </c>
       <c r="G1300" s="40">
         <v>57.475900000000003</v>
       </c>
       <c r="H1300" s="40">
-        <v>10520.786973322731</v>
+        <v>10543.351213291135</v>
       </c>
       <c r="I1300" s="41">
-        <v>7146.7869866833389</v>
+        <v>7150.6258724740437</v>
       </c>
       <c r="J1300" s="40">
-        <v>4604.3046999999997</v>
+        <v>4604.5807999999997</v>
       </c>
       <c r="K1300" s="40"/>
       <c r="L1300" s="40"/>
       <c r="M1300" s="40"/>
       <c r="N1300" s="40">
-        <v>35999.839099999997</v>
+        <v>35702.454199999993</v>
       </c>
     </row>
     <row r="1301" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58930,37 +58930,37 @@
         <v>46305</v>
       </c>
       <c r="B1301" s="40">
-        <v>46833.122000000003</v>
+        <v>50640.489200000004</v>
       </c>
       <c r="C1301" s="40">
-        <v>8556.9856</v>
+        <v>9376.9570999999996</v>
       </c>
       <c r="D1301" s="40">
-        <v>5473.086456987844</v>
+        <v>5400.5247821812054</v>
       </c>
       <c r="E1301" s="41">
-        <v>5893.0250562346109</v>
+        <v>5863.5404864747579</v>
       </c>
       <c r="F1301" s="40">
-        <v>1017.8108999999999</v>
+        <v>1566.192</v>
       </c>
       <c r="G1301" s="40">
-        <v>157.3793</v>
+        <v>233.31800000000001</v>
       </c>
       <c r="H1301" s="40">
-        <v>6467.2475986359068</v>
+        <v>6712.692548367464</v>
       </c>
       <c r="I1301" s="41">
-        <v>7099.9597677194879</v>
+        <v>7119.7442163663145</v>
       </c>
       <c r="J1301" s="40">
-        <v>6030.6569</v>
+        <v>6287.9677000000001</v>
       </c>
       <c r="K1301" s="40"/>
       <c r="L1301" s="40"/>
       <c r="M1301" s="40"/>
       <c r="N1301" s="40">
-        <v>53881.589800000002</v>
+        <v>58494.648900000007</v>
       </c>
     </row>
     <row r="1302" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -58968,54 +58968,76 @@
         <v>46312</v>
       </c>
       <c r="B1302" s="40">
-        <v>26327.8783</v>
+        <v>40930.171999999999</v>
       </c>
       <c r="C1302" s="40">
-        <v>3539.2494000000002</v>
+        <v>6054.2332999999999</v>
       </c>
       <c r="D1302" s="40">
-        <v>7438.8310414066891</v>
+        <v>6760.5871745973191</v>
       </c>
       <c r="E1302" s="41">
-        <v>5971.5395754024476</v>
+        <v>5929.8512572238396</v>
       </c>
       <c r="F1302" s="40">
-        <v>361.16469999999998</v>
+        <v>443.89260000000002</v>
       </c>
       <c r="G1302" s="40">
-        <v>52.304699999999997</v>
+        <v>59.290199999999999</v>
       </c>
       <c r="H1302" s="40">
-        <v>6905.0142721399789</v>
+        <v>7486.7785907283169</v>
       </c>
       <c r="I1302" s="41">
-        <v>6843.8516060566944</v>
+        <v>6968.6825078927168</v>
       </c>
       <c r="J1302" s="40">
-        <v>2177.6768000000002</v>
+        <v>4114.0347000000002</v>
       </c>
       <c r="K1302" s="40"/>
       <c r="L1302" s="40"/>
       <c r="M1302" s="40"/>
       <c r="N1302" s="40">
-        <v>28866.719799999999</v>
+        <v>45488.099299999994</v>
       </c>
     </row>
     <row r="1303" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1303" s="39"/>
-      <c r="B1303" s="40"/>
-      <c r="C1303" s="40"/>
-      <c r="D1303" s="40"/>
-      <c r="E1303" s="41"/>
-      <c r="F1303" s="40"/>
-      <c r="G1303" s="40"/>
-      <c r="H1303" s="40"/>
-      <c r="I1303" s="41"/>
-      <c r="J1303" s="40"/>
+      <c r="A1303" s="39">
+        <v>46319</v>
+      </c>
+      <c r="B1303" s="40">
+        <v>29555.0978</v>
+      </c>
+      <c r="C1303" s="40">
+        <v>5092.6455999999998</v>
+      </c>
+      <c r="D1303" s="40">
+        <v>5803.4860701871739</v>
+      </c>
+      <c r="E1303" s="41">
+        <v>5965.2370768382652</v>
+      </c>
+      <c r="F1303" s="40">
+        <v>859.07060000000001</v>
+      </c>
+      <c r="G1303" s="40">
+        <v>82.044899999999998</v>
+      </c>
+      <c r="H1303" s="40">
+        <v>10470.737364540635</v>
+      </c>
+      <c r="I1303" s="41">
+        <v>7899.751664626795</v>
+      </c>
+      <c r="J1303" s="40">
+        <v>3731.8847000000001</v>
+      </c>
       <c r="K1303" s="40"/>
       <c r="L1303" s="40"/>
       <c r="M1303" s="40"/>
-      <c r="N1303" s="40"/>
+      <c r="N1303" s="40">
+        <v>34146.053099999997</v>
+      </c>
     </row>
     <row r="1304" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1304" s="39"/>
